--- a/data-sources/战斗技能等级表.xlsx
+++ b/data-sources/战斗技能等级表.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\策划\1.表格目录\XLS表格\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\古荒遗迹2策划\1.表格目录\XLS表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="SkillLevel" sheetId="2" r:id="rId1"/>
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9852" uniqueCount="1044">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9852" uniqueCount="1006">
   <si>
     <t>技能ID</t>
   </si>
@@ -3084,120 +3084,6 @@
   </si>
   <si>
     <t>幻影造成原技能伤害的{0}</t>
-  </si>
-  <si>
-    <t>[[0.30]]</t>
-  </si>
-  <si>
-    <t>[[0.35]]</t>
-  </si>
-  <si>
-    <t>[[0.40]]</t>
-  </si>
-  <si>
-    <t>[[0.50]]</t>
-  </si>
-  <si>
-    <t>[[0.60]]</t>
-  </si>
-  <si>
-    <t>[[0.65]]</t>
-  </si>
-  <si>
-    <t>[[0.70]]</t>
-  </si>
-  <si>
-    <t>[[0.75]]</t>
-  </si>
-  <si>
-    <t>[[0.80]]</t>
-  </si>
-  <si>
-    <t>[[0.85]]</t>
-  </si>
-  <si>
-    <t>[[0.90]]</t>
-  </si>
-  <si>
-    <t>[[0.95]]</t>
-  </si>
-  <si>
-    <t>[[1.00]]</t>
-  </si>
-  <si>
-    <t>[[1.05]]</t>
-  </si>
-  <si>
-    <t>[[1.10]]</t>
-  </si>
-  <si>
-    <t>[[1.15]]</t>
-  </si>
-  <si>
-    <t>[[1.20]]</t>
-  </si>
-  <si>
-    <t>[[1.25]]</t>
-  </si>
-  <si>
-    <t>[[1.30]]</t>
-  </si>
-  <si>
-    <t>[[1.35]]</t>
-  </si>
-  <si>
-    <t>[[1.40]]</t>
-  </si>
-  <si>
-    <t>[[1.45]]</t>
-  </si>
-  <si>
-    <t>[[1.50]]</t>
-  </si>
-  <si>
-    <t>[[1.55]]</t>
-  </si>
-  <si>
-    <t>[[1.60]]</t>
-  </si>
-  <si>
-    <t>[[1.65]]</t>
-  </si>
-  <si>
-    <t>[[1.70]]</t>
-  </si>
-  <si>
-    <t>[[1.75]]</t>
-  </si>
-  <si>
-    <t>[[1.80]]</t>
-  </si>
-  <si>
-    <t>[[1.85]]</t>
-  </si>
-  <si>
-    <t>[[1.90]]</t>
-  </si>
-  <si>
-    <t>[[1.95]]</t>
-  </si>
-  <si>
-    <t>[[2.00]]</t>
-  </si>
-  <si>
-    <t>[[2.05]]</t>
-  </si>
-  <si>
-    <t>[[2.10]]</t>
-  </si>
-  <si>
-    <t>[[2.15]]</t>
-  </si>
-  <si>
-    <t>[[2.20]]</t>
-  </si>
-  <si>
-    <t>[[2.25]]</t>
   </si>
   <si>
     <t>移动速度增加{0}</t>
@@ -65022,7 +64908,7 @@
         <v>893</v>
       </c>
       <c r="F372" s="25" t="s">
-        <v>970</v>
+        <v>894</v>
       </c>
     </row>
     <row r="373" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65040,7 +64926,7 @@
         <v>893</v>
       </c>
       <c r="F373" s="25" t="s">
-        <v>971</v>
+        <v>895</v>
       </c>
     </row>
     <row r="374" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65058,7 +64944,7 @@
         <v>893</v>
       </c>
       <c r="F374" s="25" t="s">
-        <v>972</v>
+        <v>896</v>
       </c>
     </row>
     <row r="375" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65076,7 +64962,7 @@
         <v>893</v>
       </c>
       <c r="F375" s="25" t="s">
-        <v>933</v>
+        <v>897</v>
       </c>
     </row>
     <row r="376" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65094,7 +64980,7 @@
         <v>893</v>
       </c>
       <c r="F376" s="25" t="s">
-        <v>973</v>
+        <v>898</v>
       </c>
     </row>
     <row r="377" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65112,7 +64998,7 @@
         <v>893</v>
       </c>
       <c r="F377" s="25" t="s">
-        <v>923</v>
+        <v>899</v>
       </c>
     </row>
     <row r="378" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65130,7 +65016,7 @@
         <v>893</v>
       </c>
       <c r="F378" s="25" t="s">
-        <v>974</v>
+        <v>900</v>
       </c>
     </row>
     <row r="379" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65148,7 +65034,7 @@
         <v>893</v>
       </c>
       <c r="F379" s="25" t="s">
-        <v>975</v>
+        <v>901</v>
       </c>
     </row>
     <row r="380" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65166,7 +65052,7 @@
         <v>893</v>
       </c>
       <c r="F380" s="25" t="s">
-        <v>976</v>
+        <v>902</v>
       </c>
     </row>
     <row r="381" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65184,7 +65070,7 @@
         <v>893</v>
       </c>
       <c r="F381" s="25" t="s">
-        <v>977</v>
+        <v>903</v>
       </c>
     </row>
     <row r="382" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65202,7 +65088,7 @@
         <v>893</v>
       </c>
       <c r="F382" s="25" t="s">
-        <v>978</v>
+        <v>904</v>
       </c>
     </row>
     <row r="383" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65220,7 +65106,7 @@
         <v>893</v>
       </c>
       <c r="F383" s="25" t="s">
-        <v>979</v>
+        <v>905</v>
       </c>
     </row>
     <row r="384" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65238,7 +65124,7 @@
         <v>893</v>
       </c>
       <c r="F384" s="25" t="s">
-        <v>980</v>
+        <v>906</v>
       </c>
     </row>
     <row r="385" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65256,7 +65142,7 @@
         <v>893</v>
       </c>
       <c r="F385" s="25" t="s">
-        <v>981</v>
+        <v>907</v>
       </c>
     </row>
     <row r="386" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65274,7 +65160,7 @@
         <v>893</v>
       </c>
       <c r="F386" s="25" t="s">
-        <v>982</v>
+        <v>908</v>
       </c>
     </row>
     <row r="387" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65292,7 +65178,7 @@
         <v>893</v>
       </c>
       <c r="F387" s="25" t="s">
-        <v>983</v>
+        <v>909</v>
       </c>
     </row>
     <row r="388" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65310,7 +65196,7 @@
         <v>893</v>
       </c>
       <c r="F388" s="25" t="s">
-        <v>984</v>
+        <v>910</v>
       </c>
     </row>
     <row r="389" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65328,7 +65214,7 @@
         <v>893</v>
       </c>
       <c r="F389" s="25" t="s">
-        <v>985</v>
+        <v>911</v>
       </c>
     </row>
     <row r="390" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65346,7 +65232,7 @@
         <v>893</v>
       </c>
       <c r="F390" s="25" t="s">
-        <v>986</v>
+        <v>912</v>
       </c>
     </row>
     <row r="391" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65364,7 +65250,7 @@
         <v>893</v>
       </c>
       <c r="F391" s="25" t="s">
-        <v>987</v>
+        <v>913</v>
       </c>
     </row>
     <row r="392" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65382,7 +65268,7 @@
         <v>893</v>
       </c>
       <c r="F392" s="25" t="s">
-        <v>988</v>
+        <v>913</v>
       </c>
     </row>
     <row r="393" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65400,7 +65286,7 @@
         <v>893</v>
       </c>
       <c r="F393" s="25" t="s">
-        <v>989</v>
+        <v>913</v>
       </c>
     </row>
     <row r="394" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65418,7 +65304,7 @@
         <v>893</v>
       </c>
       <c r="F394" s="25" t="s">
-        <v>990</v>
+        <v>913</v>
       </c>
     </row>
     <row r="395" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65436,7 +65322,7 @@
         <v>893</v>
       </c>
       <c r="F395" s="25" t="s">
-        <v>991</v>
+        <v>913</v>
       </c>
     </row>
     <row r="396" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65454,7 +65340,7 @@
         <v>893</v>
       </c>
       <c r="F396" s="25" t="s">
-        <v>992</v>
+        <v>913</v>
       </c>
     </row>
     <row r="397" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65472,7 +65358,7 @@
         <v>893</v>
       </c>
       <c r="F397" s="25" t="s">
-        <v>993</v>
+        <v>913</v>
       </c>
     </row>
     <row r="398" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65490,7 +65376,7 @@
         <v>893</v>
       </c>
       <c r="F398" s="25" t="s">
-        <v>994</v>
+        <v>913</v>
       </c>
     </row>
     <row r="399" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65508,7 +65394,7 @@
         <v>893</v>
       </c>
       <c r="F399" s="25" t="s">
-        <v>995</v>
+        <v>913</v>
       </c>
     </row>
     <row r="400" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65526,7 +65412,7 @@
         <v>893</v>
       </c>
       <c r="F400" s="25" t="s">
-        <v>996</v>
+        <v>913</v>
       </c>
     </row>
     <row r="401" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65544,7 +65430,7 @@
         <v>893</v>
       </c>
       <c r="F401" s="25" t="s">
-        <v>997</v>
+        <v>913</v>
       </c>
     </row>
     <row r="402" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65562,7 +65448,7 @@
         <v>893</v>
       </c>
       <c r="F402" s="25" t="s">
-        <v>998</v>
+        <v>913</v>
       </c>
     </row>
     <row r="403" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65580,7 +65466,7 @@
         <v>893</v>
       </c>
       <c r="F403" s="25" t="s">
-        <v>999</v>
+        <v>913</v>
       </c>
     </row>
     <row r="404" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65598,7 +65484,7 @@
         <v>893</v>
       </c>
       <c r="F404" s="25" t="s">
-        <v>1000</v>
+        <v>913</v>
       </c>
     </row>
     <row r="405" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65616,7 +65502,7 @@
         <v>893</v>
       </c>
       <c r="F405" s="25" t="s">
-        <v>1001</v>
+        <v>913</v>
       </c>
     </row>
     <row r="406" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65634,7 +65520,7 @@
         <v>893</v>
       </c>
       <c r="F406" s="25" t="s">
-        <v>1002</v>
+        <v>913</v>
       </c>
     </row>
     <row r="407" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65652,7 +65538,7 @@
         <v>893</v>
       </c>
       <c r="F407" s="25" t="s">
-        <v>1003</v>
+        <v>913</v>
       </c>
     </row>
     <row r="408" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65670,7 +65556,7 @@
         <v>893</v>
       </c>
       <c r="F408" s="25" t="s">
-        <v>1004</v>
+        <v>913</v>
       </c>
     </row>
     <row r="409" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65688,7 +65574,7 @@
         <v>893</v>
       </c>
       <c r="F409" s="25" t="s">
-        <v>1005</v>
+        <v>913</v>
       </c>
     </row>
     <row r="410" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65706,7 +65592,7 @@
         <v>893</v>
       </c>
       <c r="F410" s="25" t="s">
-        <v>1006</v>
+        <v>913</v>
       </c>
     </row>
     <row r="411" s="1" customFormat="1" ht="16.5" spans="1:6">
@@ -65724,7 +65610,7 @@
         <v>893</v>
       </c>
       <c r="F411" s="25" t="s">
-        <v>1007</v>
+        <v>913</v>
       </c>
     </row>
     <row r="412" ht="16.5" spans="1:6">
@@ -65735,10 +65621,10 @@
         <v>1</v>
       </c>
       <c r="C412" t="s">
-        <v>1008</v>
+        <v>970</v>
       </c>
       <c r="D412" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E412" t="s">
         <v>893</v>
@@ -65755,7 +65641,7 @@
         <v>2</v>
       </c>
       <c r="D413" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E413" t="s">
         <v>893</v>
@@ -65772,7 +65658,7 @@
         <v>3</v>
       </c>
       <c r="D414" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E414" t="s">
         <v>893</v>
@@ -65789,7 +65675,7 @@
         <v>4</v>
       </c>
       <c r="D415" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E415" t="s">
         <v>893</v>
@@ -65806,7 +65692,7 @@
         <v>5</v>
       </c>
       <c r="D416" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E416" t="s">
         <v>893</v>
@@ -65823,7 +65709,7 @@
         <v>6</v>
       </c>
       <c r="D417" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E417" t="s">
         <v>893</v>
@@ -65840,7 +65726,7 @@
         <v>7</v>
       </c>
       <c r="D418" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E418" t="s">
         <v>893</v>
@@ -65857,7 +65743,7 @@
         <v>8</v>
       </c>
       <c r="D419" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E419" t="s">
         <v>893</v>
@@ -65874,7 +65760,7 @@
         <v>9</v>
       </c>
       <c r="D420" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E420" t="s">
         <v>893</v>
@@ -65891,7 +65777,7 @@
         <v>10</v>
       </c>
       <c r="D421" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E421" t="s">
         <v>893</v>
@@ -65908,7 +65794,7 @@
         <v>11</v>
       </c>
       <c r="D422" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E422" t="s">
         <v>893</v>
@@ -65925,7 +65811,7 @@
         <v>12</v>
       </c>
       <c r="D423" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E423" t="s">
         <v>893</v>
@@ -65942,7 +65828,7 @@
         <v>13</v>
       </c>
       <c r="D424" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E424" t="s">
         <v>893</v>
@@ -65959,7 +65845,7 @@
         <v>14</v>
       </c>
       <c r="D425" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E425" t="s">
         <v>893</v>
@@ -65976,7 +65862,7 @@
         <v>15</v>
       </c>
       <c r="D426" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E426" t="s">
         <v>893</v>
@@ -65993,7 +65879,7 @@
         <v>16</v>
       </c>
       <c r="D427" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E427" t="s">
         <v>893</v>
@@ -66010,7 +65896,7 @@
         <v>17</v>
       </c>
       <c r="D428" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E428" t="s">
         <v>893</v>
@@ -66027,7 +65913,7 @@
         <v>18</v>
       </c>
       <c r="D429" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E429" t="s">
         <v>893</v>
@@ -66044,7 +65930,7 @@
         <v>19</v>
       </c>
       <c r="D430" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E430" t="s">
         <v>893</v>
@@ -66061,7 +65947,7 @@
         <v>20</v>
       </c>
       <c r="D431" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E431" t="s">
         <v>893</v>
@@ -66078,7 +65964,7 @@
         <v>21</v>
       </c>
       <c r="D432" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E432" t="s">
         <v>893</v>
@@ -66095,7 +65981,7 @@
         <v>22</v>
       </c>
       <c r="D433" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E433" t="s">
         <v>893</v>
@@ -66112,7 +65998,7 @@
         <v>23</v>
       </c>
       <c r="D434" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E434" t="s">
         <v>893</v>
@@ -66129,7 +66015,7 @@
         <v>24</v>
       </c>
       <c r="D435" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E435" t="s">
         <v>893</v>
@@ -66146,7 +66032,7 @@
         <v>25</v>
       </c>
       <c r="D436" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E436" t="s">
         <v>893</v>
@@ -66163,7 +66049,7 @@
         <v>26</v>
       </c>
       <c r="D437" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E437" t="s">
         <v>893</v>
@@ -66180,7 +66066,7 @@
         <v>27</v>
       </c>
       <c r="D438" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E438" t="s">
         <v>893</v>
@@ -66197,7 +66083,7 @@
         <v>28</v>
       </c>
       <c r="D439" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E439" t="s">
         <v>893</v>
@@ -66214,7 +66100,7 @@
         <v>29</v>
       </c>
       <c r="D440" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E440" t="s">
         <v>893</v>
@@ -66231,7 +66117,7 @@
         <v>30</v>
       </c>
       <c r="D441" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E441" t="s">
         <v>893</v>
@@ -66248,7 +66134,7 @@
         <v>31</v>
       </c>
       <c r="D442" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E442" t="s">
         <v>893</v>
@@ -66265,7 +66151,7 @@
         <v>32</v>
       </c>
       <c r="D443" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E443" t="s">
         <v>893</v>
@@ -66282,7 +66168,7 @@
         <v>33</v>
       </c>
       <c r="D444" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E444" t="s">
         <v>893</v>
@@ -66299,7 +66185,7 @@
         <v>34</v>
       </c>
       <c r="D445" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E445" t="s">
         <v>893</v>
@@ -66316,7 +66202,7 @@
         <v>35</v>
       </c>
       <c r="D446" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E446" t="s">
         <v>893</v>
@@ -66333,7 +66219,7 @@
         <v>36</v>
       </c>
       <c r="D447" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E447" t="s">
         <v>893</v>
@@ -66350,7 +66236,7 @@
         <v>37</v>
       </c>
       <c r="D448" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E448" t="s">
         <v>893</v>
@@ -66367,7 +66253,7 @@
         <v>38</v>
       </c>
       <c r="D449" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E449" t="s">
         <v>893</v>
@@ -66384,7 +66270,7 @@
         <v>39</v>
       </c>
       <c r="D450" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E450" t="s">
         <v>893</v>
@@ -66401,7 +66287,7 @@
         <v>40</v>
       </c>
       <c r="D451" t="s">
-        <v>1009</v>
+        <v>971</v>
       </c>
       <c r="E451" t="s">
         <v>893</v>
@@ -66418,10 +66304,10 @@
         <v>1</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>1010</v>
+        <v>972</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>893</v>
@@ -66439,7 +66325,7 @@
       </c>
       <c r="C453" s="1"/>
       <c r="D453" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>893</v>
@@ -66457,7 +66343,7 @@
       </c>
       <c r="C454" s="1"/>
       <c r="D454" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>893</v>
@@ -66475,7 +66361,7 @@
       </c>
       <c r="C455" s="1"/>
       <c r="D455" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>893</v>
@@ -66493,7 +66379,7 @@
       </c>
       <c r="C456" s="1"/>
       <c r="D456" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>893</v>
@@ -66511,7 +66397,7 @@
       </c>
       <c r="C457" s="1"/>
       <c r="D457" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>893</v>
@@ -66529,7 +66415,7 @@
       </c>
       <c r="C458" s="1"/>
       <c r="D458" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>893</v>
@@ -66547,7 +66433,7 @@
       </c>
       <c r="C459" s="1"/>
       <c r="D459" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>893</v>
@@ -66565,7 +66451,7 @@
       </c>
       <c r="C460" s="1"/>
       <c r="D460" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>893</v>
@@ -66583,7 +66469,7 @@
       </c>
       <c r="C461" s="1"/>
       <c r="D461" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>893</v>
@@ -66601,7 +66487,7 @@
       </c>
       <c r="C462" s="1"/>
       <c r="D462" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>893</v>
@@ -66619,7 +66505,7 @@
       </c>
       <c r="C463" s="1"/>
       <c r="D463" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>893</v>
@@ -66637,7 +66523,7 @@
       </c>
       <c r="C464" s="1"/>
       <c r="D464" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>893</v>
@@ -66655,7 +66541,7 @@
       </c>
       <c r="C465" s="1"/>
       <c r="D465" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>893</v>
@@ -66673,7 +66559,7 @@
       </c>
       <c r="C466" s="1"/>
       <c r="D466" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>893</v>
@@ -66691,7 +66577,7 @@
       </c>
       <c r="C467" s="1"/>
       <c r="D467" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>893</v>
@@ -66709,7 +66595,7 @@
       </c>
       <c r="C468" s="1"/>
       <c r="D468" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>893</v>
@@ -66727,7 +66613,7 @@
       </c>
       <c r="C469" s="1"/>
       <c r="D469" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E469" s="1" t="s">
         <v>893</v>
@@ -66745,7 +66631,7 @@
       </c>
       <c r="C470" s="1"/>
       <c r="D470" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>893</v>
@@ -66763,7 +66649,7 @@
       </c>
       <c r="C471" s="1"/>
       <c r="D471" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E471" s="1" t="s">
         <v>893</v>
@@ -66781,7 +66667,7 @@
       </c>
       <c r="C472" s="1"/>
       <c r="D472" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E472" s="1" t="s">
         <v>893</v>
@@ -66799,7 +66685,7 @@
       </c>
       <c r="C473" s="1"/>
       <c r="D473" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E473" s="1" t="s">
         <v>893</v>
@@ -66817,7 +66703,7 @@
       </c>
       <c r="C474" s="1"/>
       <c r="D474" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E474" s="1" t="s">
         <v>893</v>
@@ -66835,7 +66721,7 @@
       </c>
       <c r="C475" s="1"/>
       <c r="D475" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E475" s="1" t="s">
         <v>893</v>
@@ -66853,7 +66739,7 @@
       </c>
       <c r="C476" s="1"/>
       <c r="D476" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E476" s="1" t="s">
         <v>893</v>
@@ -66871,7 +66757,7 @@
       </c>
       <c r="C477" s="1"/>
       <c r="D477" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>893</v>
@@ -66889,7 +66775,7 @@
       </c>
       <c r="C478" s="1"/>
       <c r="D478" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>893</v>
@@ -66907,7 +66793,7 @@
       </c>
       <c r="C479" s="1"/>
       <c r="D479" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>893</v>
@@ -66925,7 +66811,7 @@
       </c>
       <c r="C480" s="1"/>
       <c r="D480" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>893</v>
@@ -66943,7 +66829,7 @@
       </c>
       <c r="C481" s="1"/>
       <c r="D481" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E481" s="1" t="s">
         <v>893</v>
@@ -66961,7 +66847,7 @@
       </c>
       <c r="C482" s="1"/>
       <c r="D482" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E482" s="1" t="s">
         <v>893</v>
@@ -66979,7 +66865,7 @@
       </c>
       <c r="C483" s="1"/>
       <c r="D483" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>893</v>
@@ -66997,7 +66883,7 @@
       </c>
       <c r="C484" s="1"/>
       <c r="D484" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>893</v>
@@ -67015,7 +66901,7 @@
       </c>
       <c r="C485" s="1"/>
       <c r="D485" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>893</v>
@@ -67033,7 +66919,7 @@
       </c>
       <c r="C486" s="1"/>
       <c r="D486" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>893</v>
@@ -67051,7 +66937,7 @@
       </c>
       <c r="C487" s="1"/>
       <c r="D487" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>893</v>
@@ -67069,7 +66955,7 @@
       </c>
       <c r="C488" s="1"/>
       <c r="D488" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>893</v>
@@ -67087,7 +66973,7 @@
       </c>
       <c r="C489" s="1"/>
       <c r="D489" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>893</v>
@@ -67105,7 +66991,7 @@
       </c>
       <c r="C490" s="1"/>
       <c r="D490" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E490" s="1" t="s">
         <v>893</v>
@@ -67123,7 +67009,7 @@
       </c>
       <c r="C491" s="1"/>
       <c r="D491" s="1" t="s">
-        <v>1011</v>
+        <v>973</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>893</v>
@@ -67140,10 +67026,10 @@
         <v>1</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>1012</v>
+        <v>974</v>
       </c>
       <c r="D492" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E492" t="s">
         <v>893</v>
@@ -67161,7 +67047,7 @@
       </c>
       <c r="C493" s="1"/>
       <c r="D493" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E493" t="s">
         <v>893</v>
@@ -67179,7 +67065,7 @@
       </c>
       <c r="C494" s="1"/>
       <c r="D494" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E494" t="s">
         <v>893</v>
@@ -67197,7 +67083,7 @@
       </c>
       <c r="C495" s="1"/>
       <c r="D495" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E495" t="s">
         <v>893</v>
@@ -67215,7 +67101,7 @@
       </c>
       <c r="C496" s="1"/>
       <c r="D496" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E496" t="s">
         <v>893</v>
@@ -67233,7 +67119,7 @@
       </c>
       <c r="C497" s="1"/>
       <c r="D497" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E497" t="s">
         <v>893</v>
@@ -67251,7 +67137,7 @@
       </c>
       <c r="C498" s="1"/>
       <c r="D498" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E498" t="s">
         <v>893</v>
@@ -67269,7 +67155,7 @@
       </c>
       <c r="C499" s="1"/>
       <c r="D499" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E499" t="s">
         <v>893</v>
@@ -67287,7 +67173,7 @@
       </c>
       <c r="C500" s="1"/>
       <c r="D500" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E500" t="s">
         <v>893</v>
@@ -67305,7 +67191,7 @@
       </c>
       <c r="C501" s="1"/>
       <c r="D501" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E501" t="s">
         <v>893</v>
@@ -67323,7 +67209,7 @@
       </c>
       <c r="C502" s="1"/>
       <c r="D502" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E502" t="s">
         <v>893</v>
@@ -67341,7 +67227,7 @@
       </c>
       <c r="C503" s="1"/>
       <c r="D503" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E503" t="s">
         <v>893</v>
@@ -67359,7 +67245,7 @@
       </c>
       <c r="C504" s="1"/>
       <c r="D504" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E504" t="s">
         <v>893</v>
@@ -67377,7 +67263,7 @@
       </c>
       <c r="C505" s="1"/>
       <c r="D505" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E505" t="s">
         <v>893</v>
@@ -67395,7 +67281,7 @@
       </c>
       <c r="C506" s="1"/>
       <c r="D506" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E506" t="s">
         <v>893</v>
@@ -67413,7 +67299,7 @@
       </c>
       <c r="C507" s="1"/>
       <c r="D507" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E507" t="s">
         <v>893</v>
@@ -67431,7 +67317,7 @@
       </c>
       <c r="C508" s="1"/>
       <c r="D508" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E508" t="s">
         <v>893</v>
@@ -67449,7 +67335,7 @@
       </c>
       <c r="C509" s="1"/>
       <c r="D509" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E509" t="s">
         <v>893</v>
@@ -67467,7 +67353,7 @@
       </c>
       <c r="C510" s="1"/>
       <c r="D510" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E510" t="s">
         <v>893</v>
@@ -67485,7 +67371,7 @@
       </c>
       <c r="C511" s="1"/>
       <c r="D511" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E511" t="s">
         <v>893</v>
@@ -67503,7 +67389,7 @@
       </c>
       <c r="C512" s="1"/>
       <c r="D512" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E512" t="s">
         <v>893</v>
@@ -67521,7 +67407,7 @@
       </c>
       <c r="C513" s="1"/>
       <c r="D513" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E513" t="s">
         <v>893</v>
@@ -67539,7 +67425,7 @@
       </c>
       <c r="C514" s="1"/>
       <c r="D514" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E514" t="s">
         <v>893</v>
@@ -67557,7 +67443,7 @@
       </c>
       <c r="C515" s="1"/>
       <c r="D515" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E515" t="s">
         <v>893</v>
@@ -67575,7 +67461,7 @@
       </c>
       <c r="C516" s="1"/>
       <c r="D516" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E516" t="s">
         <v>893</v>
@@ -67593,7 +67479,7 @@
       </c>
       <c r="C517" s="1"/>
       <c r="D517" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E517" t="s">
         <v>893</v>
@@ -67611,7 +67497,7 @@
       </c>
       <c r="C518" s="1"/>
       <c r="D518" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E518" t="s">
         <v>893</v>
@@ -67629,7 +67515,7 @@
       </c>
       <c r="C519" s="1"/>
       <c r="D519" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E519" t="s">
         <v>893</v>
@@ -67647,7 +67533,7 @@
       </c>
       <c r="C520" s="1"/>
       <c r="D520" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E520" t="s">
         <v>893</v>
@@ -67665,7 +67551,7 @@
       </c>
       <c r="C521" s="1"/>
       <c r="D521" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E521" t="s">
         <v>893</v>
@@ -67683,7 +67569,7 @@
       </c>
       <c r="C522" s="1"/>
       <c r="D522" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E522" t="s">
         <v>893</v>
@@ -67701,7 +67587,7 @@
       </c>
       <c r="C523" s="1"/>
       <c r="D523" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E523" t="s">
         <v>893</v>
@@ -67719,7 +67605,7 @@
       </c>
       <c r="C524" s="1"/>
       <c r="D524" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E524" t="s">
         <v>893</v>
@@ -67737,7 +67623,7 @@
       </c>
       <c r="C525" s="1"/>
       <c r="D525" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E525" t="s">
         <v>893</v>
@@ -67755,7 +67641,7 @@
       </c>
       <c r="C526" s="1"/>
       <c r="D526" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E526" t="s">
         <v>893</v>
@@ -67773,7 +67659,7 @@
       </c>
       <c r="C527" s="1"/>
       <c r="D527" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E527" t="s">
         <v>893</v>
@@ -67791,7 +67677,7 @@
       </c>
       <c r="C528" s="1"/>
       <c r="D528" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E528" t="s">
         <v>893</v>
@@ -67809,7 +67695,7 @@
       </c>
       <c r="C529" s="1"/>
       <c r="D529" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E529" t="s">
         <v>893</v>
@@ -67827,7 +67713,7 @@
       </c>
       <c r="C530" s="1"/>
       <c r="D530" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E530" t="s">
         <v>893</v>
@@ -67845,7 +67731,7 @@
       </c>
       <c r="C531" s="1"/>
       <c r="D531" t="s">
-        <v>1013</v>
+        <v>975</v>
       </c>
       <c r="E531" t="s">
         <v>893</v>
@@ -67862,10 +67748,10 @@
         <v>1</v>
       </c>
       <c r="C532" t="s">
-        <v>1014</v>
+        <v>976</v>
       </c>
       <c r="D532" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E532" t="s">
         <v>893</v>
@@ -67882,7 +67768,7 @@
         <v>2</v>
       </c>
       <c r="D533" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E533" t="s">
         <v>893</v>
@@ -67899,7 +67785,7 @@
         <v>3</v>
       </c>
       <c r="D534" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E534" t="s">
         <v>893</v>
@@ -67916,7 +67802,7 @@
         <v>4</v>
       </c>
       <c r="D535" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E535" t="s">
         <v>893</v>
@@ -67933,7 +67819,7 @@
         <v>5</v>
       </c>
       <c r="D536" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E536" t="s">
         <v>893</v>
@@ -67950,7 +67836,7 @@
         <v>6</v>
       </c>
       <c r="D537" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E537" t="s">
         <v>893</v>
@@ -67967,7 +67853,7 @@
         <v>7</v>
       </c>
       <c r="D538" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E538" t="s">
         <v>893</v>
@@ -67984,7 +67870,7 @@
         <v>8</v>
       </c>
       <c r="D539" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E539" t="s">
         <v>893</v>
@@ -68001,7 +67887,7 @@
         <v>9</v>
       </c>
       <c r="D540" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E540" t="s">
         <v>893</v>
@@ -68018,7 +67904,7 @@
         <v>10</v>
       </c>
       <c r="D541" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E541" t="s">
         <v>893</v>
@@ -68035,7 +67921,7 @@
         <v>11</v>
       </c>
       <c r="D542" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E542" t="s">
         <v>893</v>
@@ -68052,7 +67938,7 @@
         <v>12</v>
       </c>
       <c r="D543" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E543" t="s">
         <v>893</v>
@@ -68069,7 +67955,7 @@
         <v>13</v>
       </c>
       <c r="D544" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E544" t="s">
         <v>893</v>
@@ -68086,7 +67972,7 @@
         <v>14</v>
       </c>
       <c r="D545" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E545" t="s">
         <v>893</v>
@@ -68103,7 +67989,7 @@
         <v>15</v>
       </c>
       <c r="D546" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E546" t="s">
         <v>893</v>
@@ -68120,7 +68006,7 @@
         <v>16</v>
       </c>
       <c r="D547" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E547" t="s">
         <v>893</v>
@@ -68137,7 +68023,7 @@
         <v>17</v>
       </c>
       <c r="D548" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E548" t="s">
         <v>893</v>
@@ -68154,7 +68040,7 @@
         <v>18</v>
       </c>
       <c r="D549" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E549" t="s">
         <v>893</v>
@@ -68171,7 +68057,7 @@
         <v>19</v>
       </c>
       <c r="D550" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E550" t="s">
         <v>893</v>
@@ -68188,7 +68074,7 @@
         <v>20</v>
       </c>
       <c r="D551" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E551" t="s">
         <v>893</v>
@@ -68205,7 +68091,7 @@
         <v>21</v>
       </c>
       <c r="D552" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E552" t="s">
         <v>893</v>
@@ -68222,7 +68108,7 @@
         <v>22</v>
       </c>
       <c r="D553" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E553" t="s">
         <v>893</v>
@@ -68239,7 +68125,7 @@
         <v>23</v>
       </c>
       <c r="D554" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E554" t="s">
         <v>893</v>
@@ -68256,7 +68142,7 @@
         <v>24</v>
       </c>
       <c r="D555" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E555" t="s">
         <v>893</v>
@@ -68273,7 +68159,7 @@
         <v>25</v>
       </c>
       <c r="D556" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E556" t="s">
         <v>893</v>
@@ -68290,7 +68176,7 @@
         <v>26</v>
       </c>
       <c r="D557" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E557" t="s">
         <v>893</v>
@@ -68307,7 +68193,7 @@
         <v>27</v>
       </c>
       <c r="D558" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E558" t="s">
         <v>893</v>
@@ -68324,7 +68210,7 @@
         <v>28</v>
       </c>
       <c r="D559" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E559" t="s">
         <v>893</v>
@@ -68341,7 +68227,7 @@
         <v>29</v>
       </c>
       <c r="D560" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E560" t="s">
         <v>893</v>
@@ -68358,7 +68244,7 @@
         <v>30</v>
       </c>
       <c r="D561" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E561" t="s">
         <v>893</v>
@@ -68375,7 +68261,7 @@
         <v>31</v>
       </c>
       <c r="D562" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E562" t="s">
         <v>893</v>
@@ -68392,7 +68278,7 @@
         <v>32</v>
       </c>
       <c r="D563" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E563" t="s">
         <v>893</v>
@@ -68409,7 +68295,7 @@
         <v>33</v>
       </c>
       <c r="D564" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E564" t="s">
         <v>893</v>
@@ -68426,7 +68312,7 @@
         <v>34</v>
       </c>
       <c r="D565" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E565" t="s">
         <v>893</v>
@@ -68443,7 +68329,7 @@
         <v>35</v>
       </c>
       <c r="D566" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E566" t="s">
         <v>893</v>
@@ -68460,7 +68346,7 @@
         <v>36</v>
       </c>
       <c r="D567" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E567" t="s">
         <v>893</v>
@@ -68477,7 +68363,7 @@
         <v>37</v>
       </c>
       <c r="D568" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E568" t="s">
         <v>893</v>
@@ -68494,7 +68380,7 @@
         <v>38</v>
       </c>
       <c r="D569" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E569" t="s">
         <v>893</v>
@@ -68511,7 +68397,7 @@
         <v>39</v>
       </c>
       <c r="D570" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E570" t="s">
         <v>893</v>
@@ -68528,7 +68414,7 @@
         <v>40</v>
       </c>
       <c r="D571" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="E571" t="s">
         <v>893</v>
@@ -68545,10 +68431,10 @@
         <v>1</v>
       </c>
       <c r="C572" t="s">
-        <v>1016</v>
+        <v>978</v>
       </c>
       <c r="D572" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E572" t="s">
         <v>893</v>
@@ -68565,7 +68451,7 @@
         <v>2</v>
       </c>
       <c r="D573" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E573" t="s">
         <v>893</v>
@@ -68582,7 +68468,7 @@
         <v>3</v>
       </c>
       <c r="D574" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E574" t="s">
         <v>893</v>
@@ -68599,7 +68485,7 @@
         <v>4</v>
       </c>
       <c r="D575" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E575" t="s">
         <v>893</v>
@@ -68616,7 +68502,7 @@
         <v>5</v>
       </c>
       <c r="D576" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E576" t="s">
         <v>893</v>
@@ -68633,7 +68519,7 @@
         <v>6</v>
       </c>
       <c r="D577" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E577" t="s">
         <v>893</v>
@@ -68650,7 +68536,7 @@
         <v>7</v>
       </c>
       <c r="D578" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E578" t="s">
         <v>893</v>
@@ -68667,7 +68553,7 @@
         <v>8</v>
       </c>
       <c r="D579" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E579" t="s">
         <v>893</v>
@@ -68684,7 +68570,7 @@
         <v>9</v>
       </c>
       <c r="D580" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E580" t="s">
         <v>893</v>
@@ -68701,7 +68587,7 @@
         <v>10</v>
       </c>
       <c r="D581" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E581" t="s">
         <v>893</v>
@@ -68718,7 +68604,7 @@
         <v>11</v>
       </c>
       <c r="D582" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E582" t="s">
         <v>893</v>
@@ -68735,7 +68621,7 @@
         <v>12</v>
       </c>
       <c r="D583" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E583" t="s">
         <v>893</v>
@@ -68752,7 +68638,7 @@
         <v>13</v>
       </c>
       <c r="D584" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E584" t="s">
         <v>893</v>
@@ -68769,7 +68655,7 @@
         <v>14</v>
       </c>
       <c r="D585" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E585" t="s">
         <v>893</v>
@@ -68786,7 +68672,7 @@
         <v>15</v>
       </c>
       <c r="D586" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E586" t="s">
         <v>893</v>
@@ -68803,7 +68689,7 @@
         <v>16</v>
       </c>
       <c r="D587" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E587" t="s">
         <v>893</v>
@@ -68820,7 +68706,7 @@
         <v>17</v>
       </c>
       <c r="D588" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E588" t="s">
         <v>893</v>
@@ -68837,7 +68723,7 @@
         <v>18</v>
       </c>
       <c r="D589" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E589" t="s">
         <v>893</v>
@@ -68854,7 +68740,7 @@
         <v>19</v>
       </c>
       <c r="D590" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E590" t="s">
         <v>893</v>
@@ -68871,7 +68757,7 @@
         <v>20</v>
       </c>
       <c r="D591" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E591" t="s">
         <v>893</v>
@@ -68888,7 +68774,7 @@
         <v>21</v>
       </c>
       <c r="D592" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E592" t="s">
         <v>893</v>
@@ -68905,7 +68791,7 @@
         <v>22</v>
       </c>
       <c r="D593" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E593" t="s">
         <v>893</v>
@@ -68922,7 +68808,7 @@
         <v>23</v>
       </c>
       <c r="D594" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E594" t="s">
         <v>893</v>
@@ -68939,7 +68825,7 @@
         <v>24</v>
       </c>
       <c r="D595" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E595" t="s">
         <v>893</v>
@@ -68956,7 +68842,7 @@
         <v>25</v>
       </c>
       <c r="D596" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E596" t="s">
         <v>893</v>
@@ -68973,7 +68859,7 @@
         <v>26</v>
       </c>
       <c r="D597" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E597" t="s">
         <v>893</v>
@@ -68990,7 +68876,7 @@
         <v>27</v>
       </c>
       <c r="D598" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E598" t="s">
         <v>893</v>
@@ -69007,7 +68893,7 @@
         <v>28</v>
       </c>
       <c r="D599" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E599" t="s">
         <v>893</v>
@@ -69024,7 +68910,7 @@
         <v>29</v>
       </c>
       <c r="D600" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E600" t="s">
         <v>893</v>
@@ -69041,7 +68927,7 @@
         <v>30</v>
       </c>
       <c r="D601" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E601" t="s">
         <v>893</v>
@@ -69058,7 +68944,7 @@
         <v>31</v>
       </c>
       <c r="D602" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E602" t="s">
         <v>893</v>
@@ -69075,7 +68961,7 @@
         <v>32</v>
       </c>
       <c r="D603" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E603" t="s">
         <v>893</v>
@@ -69092,7 +68978,7 @@
         <v>33</v>
       </c>
       <c r="D604" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E604" t="s">
         <v>893</v>
@@ -69109,7 +68995,7 @@
         <v>34</v>
       </c>
       <c r="D605" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E605" t="s">
         <v>893</v>
@@ -69126,7 +69012,7 @@
         <v>35</v>
       </c>
       <c r="D606" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E606" t="s">
         <v>893</v>
@@ -69143,7 +69029,7 @@
         <v>36</v>
       </c>
       <c r="D607" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E607" t="s">
         <v>893</v>
@@ -69160,7 +69046,7 @@
         <v>37</v>
       </c>
       <c r="D608" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E608" t="s">
         <v>893</v>
@@ -69177,7 +69063,7 @@
         <v>38</v>
       </c>
       <c r="D609" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E609" t="s">
         <v>893</v>
@@ -69194,7 +69080,7 @@
         <v>39</v>
       </c>
       <c r="D610" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E610" t="s">
         <v>893</v>
@@ -69211,7 +69097,7 @@
         <v>40</v>
       </c>
       <c r="D611" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E611" t="s">
         <v>893</v>
@@ -69228,10 +69114,10 @@
         <v>1</v>
       </c>
       <c r="C612" t="s">
-        <v>1018</v>
+        <v>980</v>
       </c>
       <c r="D612" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E612" t="s">
         <v>893</v>
@@ -69248,7 +69134,7 @@
         <v>2</v>
       </c>
       <c r="D613" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E613" t="s">
         <v>893</v>
@@ -69265,7 +69151,7 @@
         <v>3</v>
       </c>
       <c r="D614" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E614" t="s">
         <v>893</v>
@@ -69282,7 +69168,7 @@
         <v>4</v>
       </c>
       <c r="D615" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E615" t="s">
         <v>893</v>
@@ -69299,7 +69185,7 @@
         <v>5</v>
       </c>
       <c r="D616" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E616" t="s">
         <v>893</v>
@@ -69316,7 +69202,7 @@
         <v>6</v>
       </c>
       <c r="D617" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E617" t="s">
         <v>893</v>
@@ -69333,7 +69219,7 @@
         <v>7</v>
       </c>
       <c r="D618" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E618" t="s">
         <v>893</v>
@@ -69350,7 +69236,7 @@
         <v>8</v>
       </c>
       <c r="D619" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E619" t="s">
         <v>893</v>
@@ -69367,7 +69253,7 @@
         <v>9</v>
       </c>
       <c r="D620" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E620" t="s">
         <v>893</v>
@@ -69384,7 +69270,7 @@
         <v>10</v>
       </c>
       <c r="D621" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E621" t="s">
         <v>893</v>
@@ -69401,7 +69287,7 @@
         <v>11</v>
       </c>
       <c r="D622" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E622" t="s">
         <v>893</v>
@@ -69418,7 +69304,7 @@
         <v>12</v>
       </c>
       <c r="D623" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E623" t="s">
         <v>893</v>
@@ -69435,7 +69321,7 @@
         <v>13</v>
       </c>
       <c r="D624" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E624" t="s">
         <v>893</v>
@@ -69452,7 +69338,7 @@
         <v>14</v>
       </c>
       <c r="D625" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E625" t="s">
         <v>893</v>
@@ -69469,7 +69355,7 @@
         <v>15</v>
       </c>
       <c r="D626" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E626" t="s">
         <v>893</v>
@@ -69486,7 +69372,7 @@
         <v>16</v>
       </c>
       <c r="D627" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E627" t="s">
         <v>893</v>
@@ -69503,7 +69389,7 @@
         <v>17</v>
       </c>
       <c r="D628" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E628" t="s">
         <v>893</v>
@@ -69520,7 +69406,7 @@
         <v>18</v>
       </c>
       <c r="D629" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E629" t="s">
         <v>893</v>
@@ -69537,7 +69423,7 @@
         <v>19</v>
       </c>
       <c r="D630" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E630" t="s">
         <v>893</v>
@@ -69554,7 +69440,7 @@
         <v>20</v>
       </c>
       <c r="D631" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E631" t="s">
         <v>893</v>
@@ -69571,7 +69457,7 @@
         <v>21</v>
       </c>
       <c r="D632" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E632" t="s">
         <v>893</v>
@@ -69588,7 +69474,7 @@
         <v>22</v>
       </c>
       <c r="D633" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E633" t="s">
         <v>893</v>
@@ -69605,7 +69491,7 @@
         <v>23</v>
       </c>
       <c r="D634" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E634" t="s">
         <v>893</v>
@@ -69622,7 +69508,7 @@
         <v>24</v>
       </c>
       <c r="D635" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E635" t="s">
         <v>893</v>
@@ -69639,7 +69525,7 @@
         <v>25</v>
       </c>
       <c r="D636" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E636" t="s">
         <v>893</v>
@@ -69656,7 +69542,7 @@
         <v>26</v>
       </c>
       <c r="D637" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E637" t="s">
         <v>893</v>
@@ -69673,7 +69559,7 @@
         <v>27</v>
       </c>
       <c r="D638" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E638" t="s">
         <v>893</v>
@@ -69690,7 +69576,7 @@
         <v>28</v>
       </c>
       <c r="D639" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E639" t="s">
         <v>893</v>
@@ -69707,7 +69593,7 @@
         <v>29</v>
       </c>
       <c r="D640" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E640" t="s">
         <v>893</v>
@@ -69724,7 +69610,7 @@
         <v>30</v>
       </c>
       <c r="D641" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E641" t="s">
         <v>893</v>
@@ -69741,7 +69627,7 @@
         <v>31</v>
       </c>
       <c r="D642" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E642" t="s">
         <v>893</v>
@@ -69758,7 +69644,7 @@
         <v>32</v>
       </c>
       <c r="D643" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E643" t="s">
         <v>893</v>
@@ -69775,7 +69661,7 @@
         <v>33</v>
       </c>
       <c r="D644" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E644" t="s">
         <v>893</v>
@@ -69792,7 +69678,7 @@
         <v>34</v>
       </c>
       <c r="D645" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E645" t="s">
         <v>893</v>
@@ -69809,7 +69695,7 @@
         <v>35</v>
       </c>
       <c r="D646" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E646" t="s">
         <v>893</v>
@@ -69826,7 +69712,7 @@
         <v>36</v>
       </c>
       <c r="D647" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E647" t="s">
         <v>893</v>
@@ -69843,7 +69729,7 @@
         <v>37</v>
       </c>
       <c r="D648" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E648" t="s">
         <v>893</v>
@@ -69860,7 +69746,7 @@
         <v>38</v>
       </c>
       <c r="D649" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E649" t="s">
         <v>893</v>
@@ -69877,7 +69763,7 @@
         <v>39</v>
       </c>
       <c r="D650" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E650" t="s">
         <v>893</v>
@@ -69894,7 +69780,7 @@
         <v>40</v>
       </c>
       <c r="D651" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="E651" t="s">
         <v>893</v>
@@ -69911,10 +69797,10 @@
         <v>1</v>
       </c>
       <c r="C652" t="s">
-        <v>1020</v>
+        <v>982</v>
       </c>
       <c r="D652" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E652" t="s">
         <v>893</v>
@@ -69931,7 +69817,7 @@
         <v>2</v>
       </c>
       <c r="D653" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E653" t="s">
         <v>893</v>
@@ -69948,7 +69834,7 @@
         <v>3</v>
       </c>
       <c r="D654" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E654" t="s">
         <v>893</v>
@@ -69965,7 +69851,7 @@
         <v>4</v>
       </c>
       <c r="D655" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E655" t="s">
         <v>893</v>
@@ -69982,7 +69868,7 @@
         <v>5</v>
       </c>
       <c r="D656" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E656" t="s">
         <v>893</v>
@@ -69999,7 +69885,7 @@
         <v>6</v>
       </c>
       <c r="D657" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E657" t="s">
         <v>893</v>
@@ -70016,7 +69902,7 @@
         <v>7</v>
       </c>
       <c r="D658" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E658" t="s">
         <v>893</v>
@@ -70033,7 +69919,7 @@
         <v>8</v>
       </c>
       <c r="D659" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E659" t="s">
         <v>893</v>
@@ -70050,7 +69936,7 @@
         <v>9</v>
       </c>
       <c r="D660" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E660" t="s">
         <v>893</v>
@@ -70067,7 +69953,7 @@
         <v>10</v>
       </c>
       <c r="D661" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E661" t="s">
         <v>893</v>
@@ -70084,7 +69970,7 @@
         <v>11</v>
       </c>
       <c r="D662" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E662" t="s">
         <v>893</v>
@@ -70101,7 +69987,7 @@
         <v>12</v>
       </c>
       <c r="D663" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E663" t="s">
         <v>893</v>
@@ -70118,7 +70004,7 @@
         <v>13</v>
       </c>
       <c r="D664" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E664" t="s">
         <v>893</v>
@@ -70135,7 +70021,7 @@
         <v>14</v>
       </c>
       <c r="D665" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E665" t="s">
         <v>893</v>
@@ -70152,7 +70038,7 @@
         <v>15</v>
       </c>
       <c r="D666" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E666" t="s">
         <v>893</v>
@@ -70169,7 +70055,7 @@
         <v>16</v>
       </c>
       <c r="D667" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E667" t="s">
         <v>893</v>
@@ -70186,7 +70072,7 @@
         <v>17</v>
       </c>
       <c r="D668" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E668" t="s">
         <v>893</v>
@@ -70203,7 +70089,7 @@
         <v>18</v>
       </c>
       <c r="D669" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E669" t="s">
         <v>893</v>
@@ -70220,7 +70106,7 @@
         <v>19</v>
       </c>
       <c r="D670" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E670" t="s">
         <v>893</v>
@@ -70237,7 +70123,7 @@
         <v>20</v>
       </c>
       <c r="D671" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E671" t="s">
         <v>893</v>
@@ -70254,7 +70140,7 @@
         <v>21</v>
       </c>
       <c r="D672" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E672" t="s">
         <v>893</v>
@@ -70271,7 +70157,7 @@
         <v>22</v>
       </c>
       <c r="D673" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E673" t="s">
         <v>893</v>
@@ -70288,7 +70174,7 @@
         <v>23</v>
       </c>
       <c r="D674" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E674" t="s">
         <v>893</v>
@@ -70305,7 +70191,7 @@
         <v>24</v>
       </c>
       <c r="D675" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E675" t="s">
         <v>893</v>
@@ -70322,7 +70208,7 @@
         <v>25</v>
       </c>
       <c r="D676" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E676" t="s">
         <v>893</v>
@@ -70339,7 +70225,7 @@
         <v>26</v>
       </c>
       <c r="D677" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E677" t="s">
         <v>893</v>
@@ -70356,7 +70242,7 @@
         <v>27</v>
       </c>
       <c r="D678" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E678" t="s">
         <v>893</v>
@@ -70373,7 +70259,7 @@
         <v>28</v>
       </c>
       <c r="D679" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E679" t="s">
         <v>893</v>
@@ -70390,7 +70276,7 @@
         <v>29</v>
       </c>
       <c r="D680" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E680" t="s">
         <v>893</v>
@@ -70407,7 +70293,7 @@
         <v>30</v>
       </c>
       <c r="D681" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E681" t="s">
         <v>893</v>
@@ -70424,7 +70310,7 @@
         <v>31</v>
       </c>
       <c r="D682" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E682" t="s">
         <v>893</v>
@@ -70441,7 +70327,7 @@
         <v>32</v>
       </c>
       <c r="D683" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E683" t="s">
         <v>893</v>
@@ -70458,7 +70344,7 @@
         <v>33</v>
       </c>
       <c r="D684" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E684" t="s">
         <v>893</v>
@@ -70475,7 +70361,7 @@
         <v>34</v>
       </c>
       <c r="D685" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E685" t="s">
         <v>893</v>
@@ -70492,7 +70378,7 @@
         <v>35</v>
       </c>
       <c r="D686" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E686" t="s">
         <v>893</v>
@@ -70509,7 +70395,7 @@
         <v>36</v>
       </c>
       <c r="D687" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E687" t="s">
         <v>893</v>
@@ -70526,7 +70412,7 @@
         <v>37</v>
       </c>
       <c r="D688" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E688" t="s">
         <v>893</v>
@@ -70543,7 +70429,7 @@
         <v>38</v>
       </c>
       <c r="D689" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E689" t="s">
         <v>893</v>
@@ -70560,7 +70446,7 @@
         <v>39</v>
       </c>
       <c r="D690" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E690" t="s">
         <v>893</v>
@@ -70577,7 +70463,7 @@
         <v>40</v>
       </c>
       <c r="D691" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="E691" t="s">
         <v>893</v>
@@ -70594,10 +70480,10 @@
         <v>1</v>
       </c>
       <c r="C692" t="s">
-        <v>1022</v>
+        <v>984</v>
       </c>
       <c r="D692" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E692" t="s">
         <v>893</v>
@@ -70614,7 +70500,7 @@
         <v>2</v>
       </c>
       <c r="D693" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E693" t="s">
         <v>893</v>
@@ -70631,7 +70517,7 @@
         <v>3</v>
       </c>
       <c r="D694" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E694" t="s">
         <v>893</v>
@@ -70648,7 +70534,7 @@
         <v>4</v>
       </c>
       <c r="D695" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E695" t="s">
         <v>893</v>
@@ -70665,7 +70551,7 @@
         <v>5</v>
       </c>
       <c r="D696" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E696" t="s">
         <v>893</v>
@@ -70682,7 +70568,7 @@
         <v>6</v>
       </c>
       <c r="D697" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E697" t="s">
         <v>893</v>
@@ -70699,7 +70585,7 @@
         <v>7</v>
       </c>
       <c r="D698" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E698" t="s">
         <v>893</v>
@@ -70716,7 +70602,7 @@
         <v>8</v>
       </c>
       <c r="D699" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E699" t="s">
         <v>893</v>
@@ -70733,7 +70619,7 @@
         <v>9</v>
       </c>
       <c r="D700" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E700" t="s">
         <v>893</v>
@@ -70750,7 +70636,7 @@
         <v>10</v>
       </c>
       <c r="D701" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E701" t="s">
         <v>893</v>
@@ -70767,7 +70653,7 @@
         <v>11</v>
       </c>
       <c r="D702" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E702" t="s">
         <v>893</v>
@@ -70784,7 +70670,7 @@
         <v>12</v>
       </c>
       <c r="D703" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E703" t="s">
         <v>893</v>
@@ -70801,7 +70687,7 @@
         <v>13</v>
       </c>
       <c r="D704" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E704" t="s">
         <v>893</v>
@@ -70818,7 +70704,7 @@
         <v>14</v>
       </c>
       <c r="D705" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E705" t="s">
         <v>893</v>
@@ -70835,7 +70721,7 @@
         <v>15</v>
       </c>
       <c r="D706" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E706" t="s">
         <v>893</v>
@@ -70852,7 +70738,7 @@
         <v>16</v>
       </c>
       <c r="D707" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E707" t="s">
         <v>893</v>
@@ -70869,7 +70755,7 @@
         <v>17</v>
       </c>
       <c r="D708" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E708" t="s">
         <v>893</v>
@@ -70886,7 +70772,7 @@
         <v>18</v>
       </c>
       <c r="D709" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E709" t="s">
         <v>893</v>
@@ -70903,7 +70789,7 @@
         <v>19</v>
       </c>
       <c r="D710" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E710" t="s">
         <v>893</v>
@@ -70920,7 +70806,7 @@
         <v>20</v>
       </c>
       <c r="D711" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E711" t="s">
         <v>893</v>
@@ -70937,7 +70823,7 @@
         <v>21</v>
       </c>
       <c r="D712" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E712" t="s">
         <v>893</v>
@@ -70954,7 +70840,7 @@
         <v>22</v>
       </c>
       <c r="D713" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E713" t="s">
         <v>893</v>
@@ -70971,7 +70857,7 @@
         <v>23</v>
       </c>
       <c r="D714" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E714" t="s">
         <v>893</v>
@@ -70988,7 +70874,7 @@
         <v>24</v>
       </c>
       <c r="D715" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E715" t="s">
         <v>893</v>
@@ -71005,7 +70891,7 @@
         <v>25</v>
       </c>
       <c r="D716" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E716" t="s">
         <v>893</v>
@@ -71022,7 +70908,7 @@
         <v>26</v>
       </c>
       <c r="D717" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E717" t="s">
         <v>893</v>
@@ -71039,7 +70925,7 @@
         <v>27</v>
       </c>
       <c r="D718" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E718" t="s">
         <v>893</v>
@@ -71056,7 +70942,7 @@
         <v>28</v>
       </c>
       <c r="D719" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E719" t="s">
         <v>893</v>
@@ -71073,7 +70959,7 @@
         <v>29</v>
       </c>
       <c r="D720" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E720" t="s">
         <v>893</v>
@@ -71090,7 +70976,7 @@
         <v>30</v>
       </c>
       <c r="D721" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E721" t="s">
         <v>893</v>
@@ -71107,7 +70993,7 @@
         <v>31</v>
       </c>
       <c r="D722" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E722" t="s">
         <v>893</v>
@@ -71124,7 +71010,7 @@
         <v>32</v>
       </c>
       <c r="D723" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E723" t="s">
         <v>893</v>
@@ -71141,7 +71027,7 @@
         <v>33</v>
       </c>
       <c r="D724" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E724" t="s">
         <v>893</v>
@@ -71158,7 +71044,7 @@
         <v>34</v>
       </c>
       <c r="D725" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E725" t="s">
         <v>893</v>
@@ -71175,7 +71061,7 @@
         <v>35</v>
       </c>
       <c r="D726" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E726" t="s">
         <v>893</v>
@@ -71192,7 +71078,7 @@
         <v>36</v>
       </c>
       <c r="D727" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E727" t="s">
         <v>893</v>
@@ -71209,7 +71095,7 @@
         <v>37</v>
       </c>
       <c r="D728" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E728" t="s">
         <v>893</v>
@@ -71226,7 +71112,7 @@
         <v>38</v>
       </c>
       <c r="D729" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E729" t="s">
         <v>893</v>
@@ -71243,7 +71129,7 @@
         <v>39</v>
       </c>
       <c r="D730" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E730" t="s">
         <v>893</v>
@@ -71260,7 +71146,7 @@
         <v>40</v>
       </c>
       <c r="D731" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E731" t="s">
         <v>893</v>
@@ -71297,36 +71183,36 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>1024</v>
+        <v>986</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1025</v>
+        <v>987</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1026</v>
+        <v>988</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1027</v>
+        <v>989</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1028</v>
+        <v>990</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>1029</v>
+        <v>991</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1030</v>
+        <v>992</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1031</v>
+        <v>993</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1032</v>
+        <v>994</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1033</v>
+        <v>995</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -71346,67 +71232,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="18" spans="1:5">
+    <row r="4" ht="16.5" spans="1:5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1034</v>
+        <v>996</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1035</v>
+        <v>997</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" ht="18" spans="1:5">
+    <row r="5" ht="16.5" spans="1:5">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1036</v>
+        <v>998</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1037</v>
+        <v>999</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" ht="18" spans="1:5">
+    <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1038</v>
+        <v>1000</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1039</v>
+        <v>1001</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="14"/>
     </row>
-    <row r="7" ht="18" spans="1:5">
+    <row r="7" ht="16.5" spans="1:5">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>1040</v>
+        <v>1002</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>1041</v>
+        <v>1003</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="17"/>
     </row>
-    <row r="8" ht="18" spans="1:5">
+    <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="1">
         <v>5</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>1042</v>
+        <v>1004</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>1043</v>
+        <v>1005</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="20"/>

--- a/data-sources/战斗技能等级表.xlsx
+++ b/data-sources/战斗技能等级表.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\zaomeng\1.表格目录\XLS表格\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\策划\1.表格目录\XLS表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11655" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SkillLevel" sheetId="2" r:id="rId1"/>
@@ -3465,12 +3465,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -16846,9 +16846,7 @@
       <c r="F484" s="36">
         <v>1</v>
       </c>
-      <c r="G484" s="36">
-        <v>1</v>
-      </c>
+      <c r="G484" s="36"/>
       <c r="H484" s="37" t="s">
         <v>22</v>
       </c>
@@ -16872,9 +16870,7 @@
       <c r="F485" s="36">
         <v>1</v>
       </c>
-      <c r="G485" s="36">
-        <v>2</v>
-      </c>
+      <c r="G485" s="36"/>
       <c r="H485" s="37" t="s">
         <v>22</v>
       </c>
@@ -16898,9 +16894,7 @@
       <c r="F486" s="36">
         <v>1</v>
       </c>
-      <c r="G486" s="36">
-        <v>3</v>
-      </c>
+      <c r="G486" s="36"/>
       <c r="H486" s="37" t="s">
         <v>22</v>
       </c>
@@ -16924,9 +16918,7 @@
       <c r="F487" s="36">
         <v>1</v>
       </c>
-      <c r="G487" s="36">
-        <v>4</v>
-      </c>
+      <c r="G487" s="36"/>
       <c r="H487" s="37" t="s">
         <v>22</v>
       </c>
@@ -16950,9 +16942,7 @@
       <c r="F488" s="36">
         <v>1</v>
       </c>
-      <c r="G488" s="36">
-        <v>5</v>
-      </c>
+      <c r="G488" s="36"/>
       <c r="H488" s="37" t="s">
         <v>22</v>
       </c>
@@ -16976,9 +16966,7 @@
       <c r="F489" s="36">
         <v>1</v>
       </c>
-      <c r="G489" s="36">
-        <v>6</v>
-      </c>
+      <c r="G489" s="36"/>
       <c r="H489" s="37" t="s">
         <v>22</v>
       </c>
@@ -17002,9 +16990,7 @@
       <c r="F490" s="36">
         <v>1</v>
       </c>
-      <c r="G490" s="36">
-        <v>7</v>
-      </c>
+      <c r="G490" s="36"/>
       <c r="H490" s="37" t="s">
         <v>22</v>
       </c>
@@ -17028,9 +17014,7 @@
       <c r="F491" s="36">
         <v>1</v>
       </c>
-      <c r="G491" s="36">
-        <v>8</v>
-      </c>
+      <c r="G491" s="36"/>
       <c r="H491" s="37" t="s">
         <v>22</v>
       </c>
@@ -17054,9 +17038,7 @@
       <c r="F492" s="36">
         <v>1</v>
       </c>
-      <c r="G492" s="36">
-        <v>9</v>
-      </c>
+      <c r="G492" s="36"/>
       <c r="H492" s="37" t="s">
         <v>22</v>
       </c>
@@ -17080,9 +17062,7 @@
       <c r="F493" s="36">
         <v>1</v>
       </c>
-      <c r="G493" s="36">
-        <v>10</v>
-      </c>
+      <c r="G493" s="36"/>
       <c r="H493" s="37" t="s">
         <v>22</v>
       </c>
@@ -17106,9 +17086,7 @@
       <c r="F494" s="36">
         <v>1</v>
       </c>
-      <c r="G494" s="36">
-        <v>11</v>
-      </c>
+      <c r="G494" s="36"/>
       <c r="H494" s="37" t="s">
         <v>22</v>
       </c>
@@ -17132,9 +17110,7 @@
       <c r="F495" s="36">
         <v>1</v>
       </c>
-      <c r="G495" s="36">
-        <v>12</v>
-      </c>
+      <c r="G495" s="36"/>
       <c r="H495" s="37" t="s">
         <v>22</v>
       </c>
@@ -17158,9 +17134,7 @@
       <c r="F496" s="36">
         <v>1</v>
       </c>
-      <c r="G496" s="36">
-        <v>13</v>
-      </c>
+      <c r="G496" s="36"/>
       <c r="H496" s="37" t="s">
         <v>22</v>
       </c>
@@ -17184,9 +17158,7 @@
       <c r="F497" s="36">
         <v>1</v>
       </c>
-      <c r="G497" s="36">
-        <v>14</v>
-      </c>
+      <c r="G497" s="36"/>
       <c r="H497" s="37" t="s">
         <v>22</v>
       </c>
@@ -17210,9 +17182,7 @@
       <c r="F498" s="36">
         <v>1</v>
       </c>
-      <c r="G498" s="36">
-        <v>15</v>
-      </c>
+      <c r="G498" s="36"/>
       <c r="H498" s="37" t="s">
         <v>22</v>
       </c>
@@ -17236,9 +17206,7 @@
       <c r="F499" s="36">
         <v>1</v>
       </c>
-      <c r="G499" s="36">
-        <v>16</v>
-      </c>
+      <c r="G499" s="36"/>
       <c r="H499" s="37" t="s">
         <v>22</v>
       </c>
@@ -17262,9 +17230,7 @@
       <c r="F500" s="36">
         <v>1</v>
       </c>
-      <c r="G500" s="36">
-        <v>17</v>
-      </c>
+      <c r="G500" s="36"/>
       <c r="H500" s="37" t="s">
         <v>22</v>
       </c>
@@ -17288,9 +17254,7 @@
       <c r="F501" s="36">
         <v>1</v>
       </c>
-      <c r="G501" s="36">
-        <v>18</v>
-      </c>
+      <c r="G501" s="36"/>
       <c r="H501" s="37" t="s">
         <v>22</v>
       </c>
@@ -17314,9 +17278,7 @@
       <c r="F502" s="36">
         <v>1</v>
       </c>
-      <c r="G502" s="36">
-        <v>19</v>
-      </c>
+      <c r="G502" s="36"/>
       <c r="H502" s="37" t="s">
         <v>22</v>
       </c>
@@ -17340,9 +17302,7 @@
       <c r="F503" s="36">
         <v>1</v>
       </c>
-      <c r="G503" s="36">
-        <v>20</v>
-      </c>
+      <c r="G503" s="36"/>
       <c r="H503" s="37" t="s">
         <v>22</v>
       </c>
@@ -17366,9 +17326,7 @@
       <c r="F504" s="36">
         <v>1</v>
       </c>
-      <c r="G504" s="36">
-        <v>21</v>
-      </c>
+      <c r="G504" s="36"/>
       <c r="H504" s="37" t="s">
         <v>23</v>
       </c>
@@ -17392,9 +17350,7 @@
       <c r="F505" s="36">
         <v>1</v>
       </c>
-      <c r="G505" s="36">
-        <v>22</v>
-      </c>
+      <c r="G505" s="36"/>
       <c r="H505" s="37" t="s">
         <v>24</v>
       </c>
@@ -17418,9 +17374,7 @@
       <c r="F506" s="36">
         <v>1</v>
       </c>
-      <c r="G506" s="36">
-        <v>23</v>
-      </c>
+      <c r="G506" s="36"/>
       <c r="H506" s="37" t="s">
         <v>25</v>
       </c>
@@ -17444,9 +17398,7 @@
       <c r="F507" s="36">
         <v>1</v>
       </c>
-      <c r="G507" s="36">
-        <v>24</v>
-      </c>
+      <c r="G507" s="36"/>
       <c r="H507" s="37" t="s">
         <v>26</v>
       </c>
@@ -17470,9 +17422,7 @@
       <c r="F508" s="36">
         <v>1</v>
       </c>
-      <c r="G508" s="36">
-        <v>25</v>
-      </c>
+      <c r="G508" s="36"/>
       <c r="H508" s="37" t="s">
         <v>27</v>
       </c>
@@ -17496,9 +17446,7 @@
       <c r="F509" s="36">
         <v>1</v>
       </c>
-      <c r="G509" s="36">
-        <v>26</v>
-      </c>
+      <c r="G509" s="36"/>
       <c r="H509" s="37" t="s">
         <v>28</v>
       </c>
@@ -17522,9 +17470,7 @@
       <c r="F510" s="36">
         <v>1</v>
       </c>
-      <c r="G510" s="36">
-        <v>27</v>
-      </c>
+      <c r="G510" s="36"/>
       <c r="H510" s="37" t="s">
         <v>29</v>
       </c>
@@ -17548,9 +17494,7 @@
       <c r="F511" s="36">
         <v>1</v>
       </c>
-      <c r="G511" s="36">
-        <v>28</v>
-      </c>
+      <c r="G511" s="36"/>
       <c r="H511" s="37" t="s">
         <v>30</v>
       </c>
@@ -17574,9 +17518,7 @@
       <c r="F512" s="36">
         <v>1</v>
       </c>
-      <c r="G512" s="36">
-        <v>29</v>
-      </c>
+      <c r="G512" s="36"/>
       <c r="H512" s="37" t="s">
         <v>31</v>
       </c>
@@ -17600,9 +17542,7 @@
       <c r="F513" s="36">
         <v>1</v>
       </c>
-      <c r="G513" s="36">
-        <v>30</v>
-      </c>
+      <c r="G513" s="36"/>
       <c r="H513" s="37" t="s">
         <v>32</v>
       </c>
@@ -17626,9 +17566,7 @@
       <c r="F514" s="36">
         <v>1</v>
       </c>
-      <c r="G514" s="36">
-        <v>31</v>
-      </c>
+      <c r="G514" s="36"/>
       <c r="H514" s="37" t="s">
         <v>33</v>
       </c>
@@ -17652,9 +17590,7 @@
       <c r="F515" s="36">
         <v>1</v>
       </c>
-      <c r="G515" s="36">
-        <v>32</v>
-      </c>
+      <c r="G515" s="36"/>
       <c r="H515" s="37" t="s">
         <v>34</v>
       </c>
@@ -17678,9 +17614,7 @@
       <c r="F516" s="36">
         <v>1</v>
       </c>
-      <c r="G516" s="36">
-        <v>33</v>
-      </c>
+      <c r="G516" s="36"/>
       <c r="H516" s="37" t="s">
         <v>35</v>
       </c>
@@ -17704,9 +17638,7 @@
       <c r="F517" s="36">
         <v>1</v>
       </c>
-      <c r="G517" s="36">
-        <v>34</v>
-      </c>
+      <c r="G517" s="36"/>
       <c r="H517" s="37" t="s">
         <v>36</v>
       </c>
@@ -17730,9 +17662,7 @@
       <c r="F518" s="36">
         <v>1</v>
       </c>
-      <c r="G518" s="36">
-        <v>35</v>
-      </c>
+      <c r="G518" s="36"/>
       <c r="H518" s="37" t="s">
         <v>37</v>
       </c>
@@ -17756,9 +17686,7 @@
       <c r="F519" s="36">
         <v>1</v>
       </c>
-      <c r="G519" s="36">
-        <v>36</v>
-      </c>
+      <c r="G519" s="36"/>
       <c r="H519" s="37" t="s">
         <v>38</v>
       </c>
@@ -17782,9 +17710,7 @@
       <c r="F520" s="36">
         <v>1</v>
       </c>
-      <c r="G520" s="36">
-        <v>37</v>
-      </c>
+      <c r="G520" s="36"/>
       <c r="H520" s="37" t="s">
         <v>39</v>
       </c>
@@ -17808,9 +17734,7 @@
       <c r="F521" s="36">
         <v>1</v>
       </c>
-      <c r="G521" s="36">
-        <v>38</v>
-      </c>
+      <c r="G521" s="36"/>
       <c r="H521" s="37" t="s">
         <v>40</v>
       </c>
@@ -17834,9 +17758,7 @@
       <c r="F522" s="36">
         <v>1</v>
       </c>
-      <c r="G522" s="36">
-        <v>39</v>
-      </c>
+      <c r="G522" s="36"/>
       <c r="H522" s="37" t="s">
         <v>41</v>
       </c>
@@ -17860,9 +17782,7 @@
       <c r="F523" s="36">
         <v>1</v>
       </c>
-      <c r="G523" s="36">
-        <v>40</v>
-      </c>
+      <c r="G523" s="36"/>
       <c r="H523" s="37" t="s">
         <v>42</v>
       </c>
@@ -17886,9 +17806,7 @@
       <c r="F524" s="36">
         <v>1</v>
       </c>
-      <c r="G524" s="39">
-        <v>1</v>
-      </c>
+      <c r="G524" s="39"/>
       <c r="H524" s="40" t="s">
         <v>22</v>
       </c>
@@ -17912,9 +17830,7 @@
       <c r="F525" s="36">
         <v>1</v>
       </c>
-      <c r="G525" s="39">
-        <v>2</v>
-      </c>
+      <c r="G525" s="39"/>
       <c r="H525" s="40" t="s">
         <v>22</v>
       </c>
@@ -17938,9 +17854,7 @@
       <c r="F526" s="36">
         <v>1</v>
       </c>
-      <c r="G526" s="39">
-        <v>3</v>
-      </c>
+      <c r="G526" s="39"/>
       <c r="H526" s="40" t="s">
         <v>22</v>
       </c>
@@ -17964,9 +17878,7 @@
       <c r="F527" s="36">
         <v>1</v>
       </c>
-      <c r="G527" s="39">
-        <v>4</v>
-      </c>
+      <c r="G527" s="39"/>
       <c r="H527" s="40" t="s">
         <v>22</v>
       </c>
@@ -17990,9 +17902,7 @@
       <c r="F528" s="36">
         <v>1</v>
       </c>
-      <c r="G528" s="39">
-        <v>5</v>
-      </c>
+      <c r="G528" s="39"/>
       <c r="H528" s="40" t="s">
         <v>22</v>
       </c>
@@ -18016,9 +17926,7 @@
       <c r="F529" s="36">
         <v>1</v>
       </c>
-      <c r="G529" s="39">
-        <v>6</v>
-      </c>
+      <c r="G529" s="39"/>
       <c r="H529" s="40" t="s">
         <v>22</v>
       </c>
@@ -18042,9 +17950,7 @@
       <c r="F530" s="36">
         <v>1</v>
       </c>
-      <c r="G530" s="39">
-        <v>7</v>
-      </c>
+      <c r="G530" s="39"/>
       <c r="H530" s="40" t="s">
         <v>22</v>
       </c>
@@ -18068,9 +17974,7 @@
       <c r="F531" s="36">
         <v>1</v>
       </c>
-      <c r="G531" s="39">
-        <v>8</v>
-      </c>
+      <c r="G531" s="39"/>
       <c r="H531" s="40" t="s">
         <v>22</v>
       </c>
@@ -18094,9 +17998,7 @@
       <c r="F532" s="36">
         <v>1</v>
       </c>
-      <c r="G532" s="39">
-        <v>9</v>
-      </c>
+      <c r="G532" s="39"/>
       <c r="H532" s="40" t="s">
         <v>22</v>
       </c>
@@ -18120,9 +18022,7 @@
       <c r="F533" s="36">
         <v>1</v>
       </c>
-      <c r="G533" s="39">
-        <v>10</v>
-      </c>
+      <c r="G533" s="39"/>
       <c r="H533" s="40" t="s">
         <v>22</v>
       </c>
@@ -18146,9 +18046,7 @@
       <c r="F534" s="36">
         <v>1</v>
       </c>
-      <c r="G534" s="39">
-        <v>11</v>
-      </c>
+      <c r="G534" s="39"/>
       <c r="H534" s="40" t="s">
         <v>22</v>
       </c>
@@ -18172,9 +18070,7 @@
       <c r="F535" s="36">
         <v>1</v>
       </c>
-      <c r="G535" s="39">
-        <v>12</v>
-      </c>
+      <c r="G535" s="39"/>
       <c r="H535" s="40" t="s">
         <v>22</v>
       </c>
@@ -18198,9 +18094,7 @@
       <c r="F536" s="36">
         <v>1</v>
       </c>
-      <c r="G536" s="39">
-        <v>13</v>
-      </c>
+      <c r="G536" s="39"/>
       <c r="H536" s="40" t="s">
         <v>22</v>
       </c>
@@ -18224,9 +18118,7 @@
       <c r="F537" s="36">
         <v>1</v>
       </c>
-      <c r="G537" s="39">
-        <v>14</v>
-      </c>
+      <c r="G537" s="39"/>
       <c r="H537" s="40" t="s">
         <v>22</v>
       </c>
@@ -18250,9 +18142,7 @@
       <c r="F538" s="36">
         <v>1</v>
       </c>
-      <c r="G538" s="39">
-        <v>15</v>
-      </c>
+      <c r="G538" s="39"/>
       <c r="H538" s="40" t="s">
         <v>22</v>
       </c>
@@ -18276,9 +18166,7 @@
       <c r="F539" s="36">
         <v>1</v>
       </c>
-      <c r="G539" s="39">
-        <v>16</v>
-      </c>
+      <c r="G539" s="39"/>
       <c r="H539" s="40" t="s">
         <v>22</v>
       </c>
@@ -18302,9 +18190,7 @@
       <c r="F540" s="36">
         <v>1</v>
       </c>
-      <c r="G540" s="39">
-        <v>17</v>
-      </c>
+      <c r="G540" s="39"/>
       <c r="H540" s="40" t="s">
         <v>22</v>
       </c>
@@ -18328,9 +18214,7 @@
       <c r="F541" s="36">
         <v>1</v>
       </c>
-      <c r="G541" s="39">
-        <v>18</v>
-      </c>
+      <c r="G541" s="39"/>
       <c r="H541" s="40" t="s">
         <v>22</v>
       </c>
@@ -18354,9 +18238,7 @@
       <c r="F542" s="36">
         <v>1</v>
       </c>
-      <c r="G542" s="39">
-        <v>19</v>
-      </c>
+      <c r="G542" s="39"/>
       <c r="H542" s="40" t="s">
         <v>22</v>
       </c>
@@ -18380,9 +18262,7 @@
       <c r="F543" s="36">
         <v>1</v>
       </c>
-      <c r="G543" s="39">
-        <v>20</v>
-      </c>
+      <c r="G543" s="39"/>
       <c r="H543" s="40" t="s">
         <v>22</v>
       </c>
@@ -18406,9 +18286,7 @@
       <c r="F544" s="36">
         <v>1</v>
       </c>
-      <c r="G544" s="39">
-        <v>21</v>
-      </c>
+      <c r="G544" s="39"/>
       <c r="H544" s="40" t="s">
         <v>23</v>
       </c>
@@ -18432,9 +18310,7 @@
       <c r="F545" s="36">
         <v>1</v>
       </c>
-      <c r="G545" s="39">
-        <v>22</v>
-      </c>
+      <c r="G545" s="39"/>
       <c r="H545" s="40" t="s">
         <v>24</v>
       </c>
@@ -18458,9 +18334,7 @@
       <c r="F546" s="36">
         <v>1</v>
       </c>
-      <c r="G546" s="39">
-        <v>23</v>
-      </c>
+      <c r="G546" s="39"/>
       <c r="H546" s="40" t="s">
         <v>25</v>
       </c>
@@ -18484,9 +18358,7 @@
       <c r="F547" s="36">
         <v>1</v>
       </c>
-      <c r="G547" s="39">
-        <v>24</v>
-      </c>
+      <c r="G547" s="39"/>
       <c r="H547" s="40" t="s">
         <v>26</v>
       </c>
@@ -18510,9 +18382,7 @@
       <c r="F548" s="36">
         <v>1</v>
       </c>
-      <c r="G548" s="39">
-        <v>25</v>
-      </c>
+      <c r="G548" s="39"/>
       <c r="H548" s="40" t="s">
         <v>27</v>
       </c>
@@ -18536,9 +18406,7 @@
       <c r="F549" s="36">
         <v>1</v>
       </c>
-      <c r="G549" s="39">
-        <v>26</v>
-      </c>
+      <c r="G549" s="39"/>
       <c r="H549" s="40" t="s">
         <v>28</v>
       </c>
@@ -18562,9 +18430,7 @@
       <c r="F550" s="36">
         <v>1</v>
       </c>
-      <c r="G550" s="39">
-        <v>27</v>
-      </c>
+      <c r="G550" s="39"/>
       <c r="H550" s="40" t="s">
         <v>29</v>
       </c>
@@ -18588,9 +18454,7 @@
       <c r="F551" s="36">
         <v>1</v>
       </c>
-      <c r="G551" s="39">
-        <v>28</v>
-      </c>
+      <c r="G551" s="39"/>
       <c r="H551" s="40" t="s">
         <v>30</v>
       </c>
@@ -18614,9 +18478,7 @@
       <c r="F552" s="36">
         <v>1</v>
       </c>
-      <c r="G552" s="39">
-        <v>29</v>
-      </c>
+      <c r="G552" s="39"/>
       <c r="H552" s="40" t="s">
         <v>31</v>
       </c>
@@ -18640,9 +18502,7 @@
       <c r="F553" s="36">
         <v>1</v>
       </c>
-      <c r="G553" s="39">
-        <v>30</v>
-      </c>
+      <c r="G553" s="39"/>
       <c r="H553" s="40" t="s">
         <v>32</v>
       </c>
@@ -18666,9 +18526,7 @@
       <c r="F554" s="36">
         <v>1</v>
       </c>
-      <c r="G554" s="39">
-        <v>31</v>
-      </c>
+      <c r="G554" s="39"/>
       <c r="H554" s="40" t="s">
         <v>33</v>
       </c>
@@ -18692,9 +18550,7 @@
       <c r="F555" s="36">
         <v>1</v>
       </c>
-      <c r="G555" s="39">
-        <v>32</v>
-      </c>
+      <c r="G555" s="39"/>
       <c r="H555" s="40" t="s">
         <v>34</v>
       </c>
@@ -18718,9 +18574,7 @@
       <c r="F556" s="36">
         <v>1</v>
       </c>
-      <c r="G556" s="39">
-        <v>33</v>
-      </c>
+      <c r="G556" s="39"/>
       <c r="H556" s="40" t="s">
         <v>35</v>
       </c>
@@ -18744,9 +18598,7 @@
       <c r="F557" s="36">
         <v>1</v>
       </c>
-      <c r="G557" s="39">
-        <v>34</v>
-      </c>
+      <c r="G557" s="39"/>
       <c r="H557" s="40" t="s">
         <v>36</v>
       </c>
@@ -18770,9 +18622,7 @@
       <c r="F558" s="36">
         <v>1</v>
       </c>
-      <c r="G558" s="39">
-        <v>35</v>
-      </c>
+      <c r="G558" s="39"/>
       <c r="H558" s="40" t="s">
         <v>37</v>
       </c>
@@ -18796,9 +18646,7 @@
       <c r="F559" s="36">
         <v>1</v>
       </c>
-      <c r="G559" s="39">
-        <v>36</v>
-      </c>
+      <c r="G559" s="39"/>
       <c r="H559" s="40" t="s">
         <v>38</v>
       </c>
@@ -18822,9 +18670,7 @@
       <c r="F560" s="36">
         <v>1</v>
       </c>
-      <c r="G560" s="39">
-        <v>37</v>
-      </c>
+      <c r="G560" s="39"/>
       <c r="H560" s="40" t="s">
         <v>39</v>
       </c>
@@ -18848,9 +18694,7 @@
       <c r="F561" s="36">
         <v>1</v>
       </c>
-      <c r="G561" s="39">
-        <v>38</v>
-      </c>
+      <c r="G561" s="39"/>
       <c r="H561" s="40" t="s">
         <v>40</v>
       </c>
@@ -18874,9 +18718,7 @@
       <c r="F562" s="36">
         <v>1</v>
       </c>
-      <c r="G562" s="39">
-        <v>39</v>
-      </c>
+      <c r="G562" s="39"/>
       <c r="H562" s="40" t="s">
         <v>41</v>
       </c>
@@ -18900,9 +18742,7 @@
       <c r="F563" s="36">
         <v>1</v>
       </c>
-      <c r="G563" s="39">
-        <v>40</v>
-      </c>
+      <c r="G563" s="39"/>
       <c r="H563" s="40" t="s">
         <v>42</v>
       </c>
@@ -18926,9 +18766,7 @@
       <c r="F564" s="36">
         <v>1</v>
       </c>
-      <c r="G564" s="36">
-        <v>1</v>
-      </c>
+      <c r="G564" s="36"/>
       <c r="H564" s="37" t="s">
         <v>22</v>
       </c>
@@ -18952,9 +18790,7 @@
       <c r="F565" s="36">
         <v>1</v>
       </c>
-      <c r="G565" s="36">
-        <v>2</v>
-      </c>
+      <c r="G565" s="36"/>
       <c r="H565" s="37" t="s">
         <v>22</v>
       </c>
@@ -18978,9 +18814,7 @@
       <c r="F566" s="36">
         <v>1</v>
       </c>
-      <c r="G566" s="36">
-        <v>3</v>
-      </c>
+      <c r="G566" s="36"/>
       <c r="H566" s="37" t="s">
         <v>22</v>
       </c>
@@ -19004,9 +18838,7 @@
       <c r="F567" s="36">
         <v>1</v>
       </c>
-      <c r="G567" s="36">
-        <v>4</v>
-      </c>
+      <c r="G567" s="36"/>
       <c r="H567" s="37" t="s">
         <v>22</v>
       </c>
@@ -19030,9 +18862,7 @@
       <c r="F568" s="36">
         <v>1</v>
       </c>
-      <c r="G568" s="36">
-        <v>5</v>
-      </c>
+      <c r="G568" s="36"/>
       <c r="H568" s="37" t="s">
         <v>22</v>
       </c>
@@ -19056,9 +18886,7 @@
       <c r="F569" s="36">
         <v>1</v>
       </c>
-      <c r="G569" s="36">
-        <v>6</v>
-      </c>
+      <c r="G569" s="36"/>
       <c r="H569" s="37" t="s">
         <v>22</v>
       </c>
@@ -19082,9 +18910,7 @@
       <c r="F570" s="36">
         <v>1</v>
       </c>
-      <c r="G570" s="36">
-        <v>7</v>
-      </c>
+      <c r="G570" s="36"/>
       <c r="H570" s="37" t="s">
         <v>22</v>
       </c>
@@ -19108,9 +18934,7 @@
       <c r="F571" s="36">
         <v>1</v>
       </c>
-      <c r="G571" s="36">
-        <v>8</v>
-      </c>
+      <c r="G571" s="36"/>
       <c r="H571" s="37" t="s">
         <v>22</v>
       </c>
@@ -19134,9 +18958,7 @@
       <c r="F572" s="36">
         <v>1</v>
       </c>
-      <c r="G572" s="36">
-        <v>9</v>
-      </c>
+      <c r="G572" s="36"/>
       <c r="H572" s="37" t="s">
         <v>22</v>
       </c>
@@ -19160,9 +18982,7 @@
       <c r="F573" s="36">
         <v>1</v>
       </c>
-      <c r="G573" s="36">
-        <v>10</v>
-      </c>
+      <c r="G573" s="36"/>
       <c r="H573" s="37" t="s">
         <v>22</v>
       </c>
@@ -19186,9 +19006,7 @@
       <c r="F574" s="36">
         <v>1</v>
       </c>
-      <c r="G574" s="36">
-        <v>11</v>
-      </c>
+      <c r="G574" s="36"/>
       <c r="H574" s="37" t="s">
         <v>22</v>
       </c>
@@ -19212,9 +19030,7 @@
       <c r="F575" s="36">
         <v>1</v>
       </c>
-      <c r="G575" s="36">
-        <v>12</v>
-      </c>
+      <c r="G575" s="36"/>
       <c r="H575" s="37" t="s">
         <v>22</v>
       </c>
@@ -19238,9 +19054,7 @@
       <c r="F576" s="36">
         <v>1</v>
       </c>
-      <c r="G576" s="36">
-        <v>13</v>
-      </c>
+      <c r="G576" s="36"/>
       <c r="H576" s="37" t="s">
         <v>22</v>
       </c>
@@ -19264,9 +19078,7 @@
       <c r="F577" s="36">
         <v>1</v>
       </c>
-      <c r="G577" s="36">
-        <v>14</v>
-      </c>
+      <c r="G577" s="36"/>
       <c r="H577" s="37" t="s">
         <v>22</v>
       </c>
@@ -19290,9 +19102,7 @@
       <c r="F578" s="36">
         <v>1</v>
       </c>
-      <c r="G578" s="36">
-        <v>15</v>
-      </c>
+      <c r="G578" s="36"/>
       <c r="H578" s="37" t="s">
         <v>22</v>
       </c>
@@ -19316,9 +19126,7 @@
       <c r="F579" s="36">
         <v>1</v>
       </c>
-      <c r="G579" s="36">
-        <v>16</v>
-      </c>
+      <c r="G579" s="36"/>
       <c r="H579" s="37" t="s">
         <v>22</v>
       </c>
@@ -19342,9 +19150,7 @@
       <c r="F580" s="36">
         <v>1</v>
       </c>
-      <c r="G580" s="36">
-        <v>17</v>
-      </c>
+      <c r="G580" s="36"/>
       <c r="H580" s="37" t="s">
         <v>22</v>
       </c>
@@ -19368,9 +19174,7 @@
       <c r="F581" s="36">
         <v>1</v>
       </c>
-      <c r="G581" s="36">
-        <v>18</v>
-      </c>
+      <c r="G581" s="36"/>
       <c r="H581" s="37" t="s">
         <v>22</v>
       </c>
@@ -19394,9 +19198,7 @@
       <c r="F582" s="36">
         <v>1</v>
       </c>
-      <c r="G582" s="36">
-        <v>19</v>
-      </c>
+      <c r="G582" s="36"/>
       <c r="H582" s="37" t="s">
         <v>22</v>
       </c>
@@ -19420,9 +19222,7 @@
       <c r="F583" s="36">
         <v>1</v>
       </c>
-      <c r="G583" s="36">
-        <v>20</v>
-      </c>
+      <c r="G583" s="36"/>
       <c r="H583" s="37" t="s">
         <v>22</v>
       </c>
@@ -19446,9 +19246,7 @@
       <c r="F584" s="36">
         <v>1</v>
       </c>
-      <c r="G584" s="36">
-        <v>21</v>
-      </c>
+      <c r="G584" s="36"/>
       <c r="H584" s="37" t="s">
         <v>23</v>
       </c>
@@ -19472,9 +19270,7 @@
       <c r="F585" s="36">
         <v>1</v>
       </c>
-      <c r="G585" s="36">
-        <v>22</v>
-      </c>
+      <c r="G585" s="36"/>
       <c r="H585" s="37" t="s">
         <v>24</v>
       </c>
@@ -19498,9 +19294,7 @@
       <c r="F586" s="36">
         <v>1</v>
       </c>
-      <c r="G586" s="36">
-        <v>23</v>
-      </c>
+      <c r="G586" s="36"/>
       <c r="H586" s="37" t="s">
         <v>25</v>
       </c>
@@ -19524,9 +19318,7 @@
       <c r="F587" s="36">
         <v>1</v>
       </c>
-      <c r="G587" s="36">
-        <v>24</v>
-      </c>
+      <c r="G587" s="36"/>
       <c r="H587" s="37" t="s">
         <v>26</v>
       </c>
@@ -19550,9 +19342,7 @@
       <c r="F588" s="36">
         <v>1</v>
       </c>
-      <c r="G588" s="36">
-        <v>25</v>
-      </c>
+      <c r="G588" s="36"/>
       <c r="H588" s="37" t="s">
         <v>27</v>
       </c>
@@ -19576,9 +19366,7 @@
       <c r="F589" s="36">
         <v>1</v>
       </c>
-      <c r="G589" s="36">
-        <v>26</v>
-      </c>
+      <c r="G589" s="36"/>
       <c r="H589" s="37" t="s">
         <v>28</v>
       </c>
@@ -19602,9 +19390,7 @@
       <c r="F590" s="36">
         <v>1</v>
       </c>
-      <c r="G590" s="36">
-        <v>27</v>
-      </c>
+      <c r="G590" s="36"/>
       <c r="H590" s="37" t="s">
         <v>29</v>
       </c>
@@ -19628,9 +19414,7 @@
       <c r="F591" s="36">
         <v>1</v>
       </c>
-      <c r="G591" s="36">
-        <v>28</v>
-      </c>
+      <c r="G591" s="36"/>
       <c r="H591" s="37" t="s">
         <v>30</v>
       </c>
@@ -19654,9 +19438,7 @@
       <c r="F592" s="36">
         <v>1</v>
       </c>
-      <c r="G592" s="36">
-        <v>29</v>
-      </c>
+      <c r="G592" s="36"/>
       <c r="H592" s="37" t="s">
         <v>31</v>
       </c>
@@ -19680,9 +19462,7 @@
       <c r="F593" s="36">
         <v>1</v>
       </c>
-      <c r="G593" s="36">
-        <v>30</v>
-      </c>
+      <c r="G593" s="36"/>
       <c r="H593" s="37" t="s">
         <v>32</v>
       </c>
@@ -19706,9 +19486,7 @@
       <c r="F594" s="36">
         <v>1</v>
       </c>
-      <c r="G594" s="36">
-        <v>31</v>
-      </c>
+      <c r="G594" s="36"/>
       <c r="H594" s="37" t="s">
         <v>33</v>
       </c>
@@ -19732,9 +19510,7 @@
       <c r="F595" s="36">
         <v>1</v>
       </c>
-      <c r="G595" s="36">
-        <v>32</v>
-      </c>
+      <c r="G595" s="36"/>
       <c r="H595" s="37" t="s">
         <v>34</v>
       </c>
@@ -19758,9 +19534,7 @@
       <c r="F596" s="36">
         <v>1</v>
       </c>
-      <c r="G596" s="36">
-        <v>33</v>
-      </c>
+      <c r="G596" s="36"/>
       <c r="H596" s="37" t="s">
         <v>35</v>
       </c>
@@ -19784,9 +19558,7 @@
       <c r="F597" s="36">
         <v>1</v>
       </c>
-      <c r="G597" s="36">
-        <v>34</v>
-      </c>
+      <c r="G597" s="36"/>
       <c r="H597" s="37" t="s">
         <v>36</v>
       </c>
@@ -19810,9 +19582,7 @@
       <c r="F598" s="36">
         <v>1</v>
       </c>
-      <c r="G598" s="36">
-        <v>35</v>
-      </c>
+      <c r="G598" s="36"/>
       <c r="H598" s="37" t="s">
         <v>37</v>
       </c>
@@ -19836,9 +19606,7 @@
       <c r="F599" s="36">
         <v>1</v>
       </c>
-      <c r="G599" s="36">
-        <v>36</v>
-      </c>
+      <c r="G599" s="36"/>
       <c r="H599" s="37" t="s">
         <v>38</v>
       </c>
@@ -19862,9 +19630,7 @@
       <c r="F600" s="36">
         <v>1</v>
       </c>
-      <c r="G600" s="36">
-        <v>37</v>
-      </c>
+      <c r="G600" s="36"/>
       <c r="H600" s="37" t="s">
         <v>39</v>
       </c>
@@ -19888,9 +19654,7 @@
       <c r="F601" s="36">
         <v>1</v>
       </c>
-      <c r="G601" s="36">
-        <v>38</v>
-      </c>
+      <c r="G601" s="36"/>
       <c r="H601" s="37" t="s">
         <v>40</v>
       </c>
@@ -19914,9 +19678,7 @@
       <c r="F602" s="36">
         <v>1</v>
       </c>
-      <c r="G602" s="36">
-        <v>39</v>
-      </c>
+      <c r="G602" s="36"/>
       <c r="H602" s="37" t="s">
         <v>41</v>
       </c>
@@ -19940,9 +19702,7 @@
       <c r="F603" s="36">
         <v>1</v>
       </c>
-      <c r="G603" s="36">
-        <v>40</v>
-      </c>
+      <c r="G603" s="36"/>
       <c r="H603" s="37" t="s">
         <v>42</v>
       </c>
@@ -21006,9 +20766,7 @@
       <c r="F644" s="36">
         <v>1</v>
       </c>
-      <c r="G644" s="36">
-        <v>1</v>
-      </c>
+      <c r="G644" s="36"/>
       <c r="H644" s="37" t="s">
         <v>22</v>
       </c>
@@ -21032,9 +20790,7 @@
       <c r="F645" s="36">
         <v>1</v>
       </c>
-      <c r="G645" s="36">
-        <v>2</v>
-      </c>
+      <c r="G645" s="36"/>
       <c r="H645" s="37" t="s">
         <v>22</v>
       </c>
@@ -21058,9 +20814,7 @@
       <c r="F646" s="36">
         <v>1</v>
       </c>
-      <c r="G646" s="36">
-        <v>3</v>
-      </c>
+      <c r="G646" s="36"/>
       <c r="H646" s="37" t="s">
         <v>22</v>
       </c>
@@ -21084,9 +20838,7 @@
       <c r="F647" s="36">
         <v>1</v>
       </c>
-      <c r="G647" s="36">
-        <v>4</v>
-      </c>
+      <c r="G647" s="36"/>
       <c r="H647" s="37" t="s">
         <v>22</v>
       </c>
@@ -21110,9 +20862,7 @@
       <c r="F648" s="36">
         <v>1</v>
       </c>
-      <c r="G648" s="36">
-        <v>5</v>
-      </c>
+      <c r="G648" s="36"/>
       <c r="H648" s="37" t="s">
         <v>22</v>
       </c>
@@ -21136,9 +20886,7 @@
       <c r="F649" s="36">
         <v>1</v>
       </c>
-      <c r="G649" s="36">
-        <v>6</v>
-      </c>
+      <c r="G649" s="36"/>
       <c r="H649" s="37" t="s">
         <v>22</v>
       </c>
@@ -21162,9 +20910,7 @@
       <c r="F650" s="36">
         <v>1</v>
       </c>
-      <c r="G650" s="36">
-        <v>7</v>
-      </c>
+      <c r="G650" s="36"/>
       <c r="H650" s="37" t="s">
         <v>22</v>
       </c>
@@ -21188,9 +20934,7 @@
       <c r="F651" s="36">
         <v>1</v>
       </c>
-      <c r="G651" s="36">
-        <v>8</v>
-      </c>
+      <c r="G651" s="36"/>
       <c r="H651" s="37" t="s">
         <v>22</v>
       </c>
@@ -21214,9 +20958,7 @@
       <c r="F652" s="36">
         <v>1</v>
       </c>
-      <c r="G652" s="36">
-        <v>9</v>
-      </c>
+      <c r="G652" s="36"/>
       <c r="H652" s="37" t="s">
         <v>22</v>
       </c>
@@ -21240,9 +20982,7 @@
       <c r="F653" s="36">
         <v>1</v>
       </c>
-      <c r="G653" s="36">
-        <v>10</v>
-      </c>
+      <c r="G653" s="36"/>
       <c r="H653" s="37" t="s">
         <v>22</v>
       </c>
@@ -21266,9 +21006,7 @@
       <c r="F654" s="36">
         <v>1</v>
       </c>
-      <c r="G654" s="36">
-        <v>11</v>
-      </c>
+      <c r="G654" s="36"/>
       <c r="H654" s="37" t="s">
         <v>22</v>
       </c>
@@ -21292,9 +21030,7 @@
       <c r="F655" s="36">
         <v>1</v>
       </c>
-      <c r="G655" s="36">
-        <v>12</v>
-      </c>
+      <c r="G655" s="36"/>
       <c r="H655" s="37" t="s">
         <v>22</v>
       </c>
@@ -21318,9 +21054,7 @@
       <c r="F656" s="36">
         <v>1</v>
       </c>
-      <c r="G656" s="36">
-        <v>13</v>
-      </c>
+      <c r="G656" s="36"/>
       <c r="H656" s="37" t="s">
         <v>22</v>
       </c>
@@ -21344,9 +21078,7 @@
       <c r="F657" s="36">
         <v>1</v>
       </c>
-      <c r="G657" s="36">
-        <v>14</v>
-      </c>
+      <c r="G657" s="36"/>
       <c r="H657" s="37" t="s">
         <v>22</v>
       </c>
@@ -21370,9 +21102,7 @@
       <c r="F658" s="36">
         <v>1</v>
       </c>
-      <c r="G658" s="36">
-        <v>15</v>
-      </c>
+      <c r="G658" s="36"/>
       <c r="H658" s="37" t="s">
         <v>22</v>
       </c>
@@ -21396,9 +21126,7 @@
       <c r="F659" s="36">
         <v>1</v>
       </c>
-      <c r="G659" s="36">
-        <v>16</v>
-      </c>
+      <c r="G659" s="36"/>
       <c r="H659" s="37" t="s">
         <v>22</v>
       </c>
@@ -21422,9 +21150,7 @@
       <c r="F660" s="36">
         <v>1</v>
       </c>
-      <c r="G660" s="36">
-        <v>17</v>
-      </c>
+      <c r="G660" s="36"/>
       <c r="H660" s="37" t="s">
         <v>22</v>
       </c>
@@ -21448,9 +21174,7 @@
       <c r="F661" s="36">
         <v>1</v>
       </c>
-      <c r="G661" s="36">
-        <v>18</v>
-      </c>
+      <c r="G661" s="36"/>
       <c r="H661" s="37" t="s">
         <v>22</v>
       </c>
@@ -21474,9 +21198,7 @@
       <c r="F662" s="36">
         <v>1</v>
       </c>
-      <c r="G662" s="36">
-        <v>19</v>
-      </c>
+      <c r="G662" s="36"/>
       <c r="H662" s="37" t="s">
         <v>22</v>
       </c>
@@ -21500,9 +21222,7 @@
       <c r="F663" s="36">
         <v>1</v>
       </c>
-      <c r="G663" s="36">
-        <v>20</v>
-      </c>
+      <c r="G663" s="36"/>
       <c r="H663" s="37" t="s">
         <v>22</v>
       </c>
@@ -21526,9 +21246,7 @@
       <c r="F664" s="36">
         <v>1</v>
       </c>
-      <c r="G664" s="36">
-        <v>21</v>
-      </c>
+      <c r="G664" s="36"/>
       <c r="H664" s="37" t="s">
         <v>23</v>
       </c>
@@ -21552,9 +21270,7 @@
       <c r="F665" s="36">
         <v>1</v>
       </c>
-      <c r="G665" s="36">
-        <v>22</v>
-      </c>
+      <c r="G665" s="36"/>
       <c r="H665" s="37" t="s">
         <v>24</v>
       </c>
@@ -21578,9 +21294,7 @@
       <c r="F666" s="36">
         <v>1</v>
       </c>
-      <c r="G666" s="36">
-        <v>23</v>
-      </c>
+      <c r="G666" s="36"/>
       <c r="H666" s="37" t="s">
         <v>25</v>
       </c>
@@ -21604,9 +21318,7 @@
       <c r="F667" s="36">
         <v>1</v>
       </c>
-      <c r="G667" s="36">
-        <v>24</v>
-      </c>
+      <c r="G667" s="36"/>
       <c r="H667" s="37" t="s">
         <v>26</v>
       </c>
@@ -21630,9 +21342,7 @@
       <c r="F668" s="36">
         <v>1</v>
       </c>
-      <c r="G668" s="36">
-        <v>25</v>
-      </c>
+      <c r="G668" s="36"/>
       <c r="H668" s="37" t="s">
         <v>27</v>
       </c>
@@ -21656,9 +21366,7 @@
       <c r="F669" s="36">
         <v>1</v>
       </c>
-      <c r="G669" s="36">
-        <v>26</v>
-      </c>
+      <c r="G669" s="36"/>
       <c r="H669" s="37" t="s">
         <v>28</v>
       </c>
@@ -21682,9 +21390,7 @@
       <c r="F670" s="36">
         <v>1</v>
       </c>
-      <c r="G670" s="36">
-        <v>27</v>
-      </c>
+      <c r="G670" s="36"/>
       <c r="H670" s="37" t="s">
         <v>29</v>
       </c>
@@ -21708,9 +21414,7 @@
       <c r="F671" s="36">
         <v>1</v>
       </c>
-      <c r="G671" s="36">
-        <v>28</v>
-      </c>
+      <c r="G671" s="36"/>
       <c r="H671" s="37" t="s">
         <v>30</v>
       </c>
@@ -21734,9 +21438,7 @@
       <c r="F672" s="36">
         <v>1</v>
       </c>
-      <c r="G672" s="36">
-        <v>29</v>
-      </c>
+      <c r="G672" s="36"/>
       <c r="H672" s="37" t="s">
         <v>31</v>
       </c>
@@ -21760,9 +21462,7 @@
       <c r="F673" s="36">
         <v>1</v>
       </c>
-      <c r="G673" s="36">
-        <v>30</v>
-      </c>
+      <c r="G673" s="36"/>
       <c r="H673" s="37" t="s">
         <v>32</v>
       </c>
@@ -21786,9 +21486,7 @@
       <c r="F674" s="36">
         <v>1</v>
       </c>
-      <c r="G674" s="36">
-        <v>31</v>
-      </c>
+      <c r="G674" s="36"/>
       <c r="H674" s="37" t="s">
         <v>33</v>
       </c>
@@ -21812,9 +21510,7 @@
       <c r="F675" s="36">
         <v>1</v>
       </c>
-      <c r="G675" s="36">
-        <v>32</v>
-      </c>
+      <c r="G675" s="36"/>
       <c r="H675" s="37" t="s">
         <v>34</v>
       </c>
@@ -21838,9 +21534,7 @@
       <c r="F676" s="36">
         <v>1</v>
       </c>
-      <c r="G676" s="36">
-        <v>33</v>
-      </c>
+      <c r="G676" s="36"/>
       <c r="H676" s="37" t="s">
         <v>35</v>
       </c>
@@ -21864,9 +21558,7 @@
       <c r="F677" s="36">
         <v>1</v>
       </c>
-      <c r="G677" s="36">
-        <v>34</v>
-      </c>
+      <c r="G677" s="36"/>
       <c r="H677" s="37" t="s">
         <v>36</v>
       </c>
@@ -21890,9 +21582,7 @@
       <c r="F678" s="36">
         <v>1</v>
       </c>
-      <c r="G678" s="36">
-        <v>35</v>
-      </c>
+      <c r="G678" s="36"/>
       <c r="H678" s="37" t="s">
         <v>37</v>
       </c>
@@ -21916,9 +21606,7 @@
       <c r="F679" s="36">
         <v>1</v>
       </c>
-      <c r="G679" s="36">
-        <v>36</v>
-      </c>
+      <c r="G679" s="36"/>
       <c r="H679" s="37" t="s">
         <v>38</v>
       </c>
@@ -21942,9 +21630,7 @@
       <c r="F680" s="36">
         <v>1</v>
       </c>
-      <c r="G680" s="36">
-        <v>37</v>
-      </c>
+      <c r="G680" s="36"/>
       <c r="H680" s="37" t="s">
         <v>39</v>
       </c>
@@ -21968,9 +21654,7 @@
       <c r="F681" s="36">
         <v>1</v>
       </c>
-      <c r="G681" s="36">
-        <v>38</v>
-      </c>
+      <c r="G681" s="36"/>
       <c r="H681" s="37" t="s">
         <v>40</v>
       </c>
@@ -21994,9 +21678,7 @@
       <c r="F682" s="36">
         <v>1</v>
       </c>
-      <c r="G682" s="36">
-        <v>39</v>
-      </c>
+      <c r="G682" s="36"/>
       <c r="H682" s="37" t="s">
         <v>41</v>
       </c>
@@ -22020,9 +21702,7 @@
       <c r="F683" s="36">
         <v>1</v>
       </c>
-      <c r="G683" s="36">
-        <v>40</v>
-      </c>
+      <c r="G683" s="36"/>
       <c r="H683" s="37" t="s">
         <v>42</v>
       </c>
